--- a/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
   <si>
     <t>APG</t>
   </si>
@@ -656,315 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43159</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1759000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1784000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1771000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1614000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1703000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1735000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1649000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1471000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1112000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1047000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>978000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>803000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>882000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>958000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>889000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>858000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>985000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1118000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1067000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>922000</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1251000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1273000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1275000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1189000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1237000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1293000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1212000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1095000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>838000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>795000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>746000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>622000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>684000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>736000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>692000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>696000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>787000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>885000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>859000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>759000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>400</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>508000</v>
+      </c>
+      <c r="E10" s="3">
         <v>511000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>496000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>425000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>466000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>442000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>437000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>376000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>274000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>252000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>232000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>181000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>198000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>222000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>197000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>162000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>198000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>233000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>208000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>163000</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -989,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1057,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1125,8 +1141,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1134,96 +1153,99 @@
         <v>13000</v>
       </c>
       <c r="E14" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F14" s="3">
         <v>4000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>12000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>24000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>9000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-4000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>208000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>12000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E15" s="3">
         <v>49000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>50000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>48000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>54000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>36000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>53000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>54000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>30000</v>
       </c>
       <c r="M15" s="3">
         <v>30000</v>
@@ -1235,34 +1257,37 @@
         <v>30000</v>
       </c>
       <c r="P15" s="3">
+        <v>30000</v>
+      </c>
+      <c r="Q15" s="3">
         <v>25000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>28000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>30000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>29000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>8000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>9000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>25000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>200</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1284,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1688000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1680000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1664000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1544000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1654000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1669000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1590000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1478000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1062000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1006000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>940000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>805000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>903000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>896000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>858000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1092000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1146000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1105000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1004000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>896000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>164900</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E18" s="3">
         <v>104000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>107000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>70000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>49000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>66000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>59000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>50000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>41000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>38000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-21000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>62000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>31000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-234000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-161000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>63000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>26000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1446,8 +1478,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1455,271 +1488,283 @@
         <v>7000</v>
       </c>
       <c r="E20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F20" s="3">
         <v>6000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>14000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>13000</v>
       </c>
       <c r="I20" s="3">
         <v>13000</v>
       </c>
       <c r="J20" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K20" s="3">
         <v>11000</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>14000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>25000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>8000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2000</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>188000</v>
+        <v>155000</v>
       </c>
       <c r="E21" s="3">
         <v>188000</v>
       </c>
       <c r="F21" s="3">
+        <v>188000</v>
+      </c>
+      <c r="G21" s="3">
         <v>149000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>142000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>152000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>148000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>80000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>98000</v>
-      </c>
-      <c r="L21" s="3">
-        <v>96000</v>
       </c>
       <c r="M21" s="3">
         <v>96000</v>
       </c>
       <c r="N21" s="3">
+        <v>96000</v>
+      </c>
+      <c r="O21" s="3">
         <v>51000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>60000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>120000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>112000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-161000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-67000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>48000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>90000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>53000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E22" s="3">
         <v>37000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>38000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>37000</v>
       </c>
       <c r="G22" s="3">
         <v>37000</v>
       </c>
       <c r="H22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="I22" s="3">
         <v>33000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>28000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>27000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>17000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>14000</v>
       </c>
       <c r="M22" s="3">
         <v>14000</v>
       </c>
       <c r="N22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="O22" s="3">
         <v>15000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>13000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>14000</v>
       </c>
       <c r="R22" s="3">
         <v>14000</v>
       </c>
       <c r="S22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="T22" s="3">
         <v>15000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>7000</v>
       </c>
       <c r="U22" s="3">
         <v>7000</v>
       </c>
       <c r="V22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="W22" s="3">
         <v>6000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>159600</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E23" s="3">
         <v>74000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>75000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>38000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>26000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>46000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>44000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-23000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>33000</v>
-      </c>
-      <c r="L23" s="3">
-        <v>30000</v>
       </c>
       <c r="M23" s="3">
         <v>30000</v>
       </c>
       <c r="N23" s="3">
+        <v>30000</v>
+      </c>
+      <c r="O23" s="3">
         <v>-14000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>55000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>24000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-245000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-151000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>14000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>57000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>22000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-159600</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1727,67 +1772,70 @@
         <v>20000</v>
       </c>
       <c r="E24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F24" s="3">
         <v>27000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>18000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-16000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>18000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-6000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>28000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-12000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-51000</v>
-      </c>
-      <c r="S24" s="3">
-        <v>2000</v>
       </c>
       <c r="T24" s="3">
         <v>2000</v>
       </c>
       <c r="U24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="V24" s="3">
         <v>4000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-159600</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1854,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E26" s="3">
         <v>54000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>48000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>26000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>22000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>28000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>30000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>21000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-22000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>27000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>36000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-194000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-153000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>12000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>53000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>21000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-159600</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-256000</v>
+      </c>
+      <c r="E27" s="3">
         <v>43000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>37000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>17000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-18000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-169000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>21000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-244000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>27000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>36000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-194000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-153000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>12000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>53000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>21000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-159600</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2058,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2126,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2194,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2262,8 +2328,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2271,135 +2340,141 @@
         <v>-7000</v>
       </c>
       <c r="E32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-6000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-14000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-13000</v>
       </c>
       <c r="I32" s="3">
         <v>-13000</v>
       </c>
       <c r="J32" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-11000</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-14000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-25000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-8000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2000</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-256000</v>
+      </c>
+      <c r="E33" s="3">
         <v>43000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>37000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>17000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-18000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-169000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>21000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-244000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>27000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>36000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-194000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-153000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>12000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>53000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>21000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-159600</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2466,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-256000</v>
+      </c>
+      <c r="E35" s="3">
         <v>43000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>37000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>17000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-18000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-169000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>21000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-244000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>27000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>36000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-194000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-153000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>12000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>53000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>21000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-159600</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43159</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2633,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2659,59 +2744,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>479000</v>
+      </c>
+      <c r="E41" s="3">
         <v>461000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>368000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>363000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>605000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>395000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>330000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>315000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1188000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1128000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>686000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>745000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>515000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>467000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>377000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>436000</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2727,8 +2813,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2795,59 +2884,62 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1831000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1810000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1827000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1711000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1772000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1760000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1712000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1636000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>984000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>947000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>848000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>747000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>781000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>906000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>891000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>913000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2863,59 +2955,62 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E44" s="3">
         <v>155000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>170000</v>
-      </c>
-      <c r="F44" s="3">
-        <v>163000</v>
       </c>
       <c r="G44" s="3">
         <v>163000</v>
       </c>
       <c r="H44" s="3">
+        <v>163000</v>
+      </c>
+      <c r="I44" s="3">
         <v>150000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>149000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>142000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>69000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>71000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>69000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>66000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>64000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>57000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>60000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>59000</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2931,59 +3026,62 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E45" s="3">
         <v>226000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>167000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>127000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>112000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>167000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>170000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>134000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>385000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>93000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>82000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>75000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>77000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>74000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>66000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>42000</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2999,59 +3097,62 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2582000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2652000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2532000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2364000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2652000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2472000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2361000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2227000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2626000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2239000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1685000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1633000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1437000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1504000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1394000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1450000</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3067,8 +3168,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3135,59 +3239,62 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>618000</v>
+      </c>
+      <c r="E48" s="3">
         <v>604000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>639000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>621000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>629000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>608000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>614000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>628000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>427000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>439000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>453000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>459000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>462000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>452000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>467000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>500000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3203,59 +3310,62 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4091000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4028000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4147000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4139000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4166000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4010000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4254000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4492000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1988000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1996000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1991000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2008000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2047000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1772000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1799000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1836000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3271,8 +3381,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3339,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3407,59 +3523,62 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>299000</v>
+      </c>
+      <c r="E52" s="3">
         <v>665000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>656000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>642000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>644000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>851000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>825000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>795000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>118000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>109000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>114000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>118000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>119000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>98000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>110000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>100000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3475,8 +3594,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3543,59 +3665,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7590000</v>
+      </c>
+      <c r="E54" s="3">
         <v>7949000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7974000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7766000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8091000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7941000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8054000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8142000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5159000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4783000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4243000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4218000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4065000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3826000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3770000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3886000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3611,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3637,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3663,59 +3792,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>472000</v>
+      </c>
+      <c r="E57" s="3">
         <v>431000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>473000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>442000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>490000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>469000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>448000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>391000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>236000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>205000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>180000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>167000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>150000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>142000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>155000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>152000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3731,59 +3861,62 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E58" s="3">
         <v>328000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>79000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>78000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>212000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>28000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>29000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>42000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>63000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>49000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>44000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>45000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>244000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3799,59 +3932,62 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1324000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1140000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1099000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1029000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1219000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1043000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>998000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>971000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>603000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>558000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>508000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>551000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>642000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>648000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>621000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>523000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,59 +4003,62 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1807000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1899000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1651000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1549000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1921000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1523000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1453000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1367000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>867000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>792000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>730000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>781000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>841000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>834000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>821000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>919000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3935,59 +4074,62 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2330000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2512000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2758000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2743000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2595000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2791000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2823000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2819000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1845000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1548000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1538000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1475000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1493000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1248000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1254000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1260000</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4003,59 +4145,62 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>585000</v>
+      </c>
+      <c r="E62" s="3">
         <v>509000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>521000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>512000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>651000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>680000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>825000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>881000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>124000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>146000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>147000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>171000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>173000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>146000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>130000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>182000</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4071,8 +4216,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4139,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4207,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4275,59 +4429,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4722000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4920000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4930000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4804000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5167000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4994000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5101000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5067000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2836000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2486000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2415000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2427000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2507000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2228000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2205000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2361000</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4343,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4369,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4437,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4505,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4532,7 +4699,7 @@
         <v>797000</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>797000</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -4573,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4641,59 +4811,62 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-36000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-90000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-138000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-164000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-186000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-214000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-255000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-237000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-252000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-271000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-292000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-284000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-262000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-289000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-325000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4703,14 +4876,17 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4777,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4845,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4913,59 +5095,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2071000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2232000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2247000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2165000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2127000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2150000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2156000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2278000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2323000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2297000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1828000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1791000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1558000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1598000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1565000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1525000</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4981,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5049,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43159</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-256000</v>
+      </c>
+      <c r="E81" s="3">
         <v>43000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>37000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>17000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-18000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-169000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>21000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-244000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>27000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>36000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-194000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-153000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>12000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>53000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>21000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-159600</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5216,8 +5413,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5225,67 +5423,70 @@
         <v>77000</v>
       </c>
       <c r="E83" s="3">
+        <v>77000</v>
+      </c>
+      <c r="F83" s="3">
         <v>75000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>74000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>79000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>73000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>76000</v>
       </c>
       <c r="J83" s="3">
         <v>76000</v>
       </c>
       <c r="K83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="L83" s="3">
         <v>48000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>52000</v>
       </c>
       <c r="M83" s="3">
         <v>52000</v>
       </c>
       <c r="N83" s="3">
+        <v>52000</v>
+      </c>
+      <c r="O83" s="3">
         <v>50000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>67000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>52000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>74000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>70000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>69000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>27000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>26000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>25000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>-5300</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5352,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5420,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5488,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5556,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5624,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>297000</v>
+      </c>
+      <c r="E89" s="3">
         <v>144000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>74000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>188000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>146000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>54000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-118000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>114000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>49000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>32000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>167000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>97000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>177000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>55000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>150000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>92000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>28000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>25000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>40000</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5718,76 +5937,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-21000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-19000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-26000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-22000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-12000</v>
       </c>
       <c r="K91" s="3">
         <v>-12000</v>
       </c>
       <c r="L91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="M91" s="3">
         <v>-9000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-18000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-14000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6000</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-11000</v>
       </c>
       <c r="S91" s="3">
         <v>-11000</v>
       </c>
       <c r="T91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="U91" s="3">
         <v>-13000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-18000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-22000</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5854,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5922,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-26000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-55000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-27000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>30000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-28000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2884000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-40000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-46000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-23000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-323000</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-1000</v>
       </c>
       <c r="Q94" s="3">
         <v>-1000</v>
       </c>
       <c r="R94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="S94" s="3">
         <v>-15000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1728000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-19000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-22000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>18600</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6016,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6084,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6152,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6220,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6288,208 +6530,220 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-279000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-21000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-16000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-216000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-17000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-45000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-13000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1831000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>288000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>442000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-36000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>223000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-235000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>139000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1398000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>25000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-19000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-16000</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5000</v>
-      </c>
-      <c r="E101" s="3">
-        <v>2000</v>
       </c>
       <c r="F101" s="3">
         <v>2000</v>
       </c>
       <c r="G101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H101" s="3">
         <v>8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-7000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
+      <c r="W101" s="3">
+        <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E102" s="3">
         <v>92000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-242000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>209000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>65000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>15000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1173000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>361000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>441000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-59000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>233000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>48000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>90000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-59000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>180000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-181000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>107000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-10000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-13000</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
   <si>
     <t>APG</t>
   </si>
@@ -656,327 +656,340 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43159</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1601000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1759000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1784000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1771000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1614000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1703000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1735000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1649000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1471000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1112000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1047000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>978000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>803000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>882000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>958000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>889000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>858000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>985000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1118000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1067000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>922000</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1109000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1251000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1273000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1275000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1189000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1237000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1293000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1212000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1095000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>838000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>795000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>746000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>622000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>684000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>736000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>692000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>696000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>787000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>885000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>859000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>759000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>400</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>492000</v>
+      </c>
+      <c r="E10" s="3">
         <v>508000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>511000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>496000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>425000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>466000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>442000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>437000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>376000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>274000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>252000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>232000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>181000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>198000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>222000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>197000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>162000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>198000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>233000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>208000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>163000</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1015,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,79 +1161,85 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E14" s="3">
         <v>13000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>37000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>12000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>24000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>9000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-11000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-4000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>208000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>12000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1224,31 +1247,31 @@
         <v>50000</v>
       </c>
       <c r="E15" s="3">
+        <v>50000</v>
+      </c>
+      <c r="F15" s="3">
         <v>49000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>50000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>48000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>54000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>36000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>53000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>54000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>32000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>30000</v>
       </c>
       <c r="N15" s="3">
         <v>30000</v>
@@ -1260,34 +1283,37 @@
         <v>30000</v>
       </c>
       <c r="Q15" s="3">
+        <v>30000</v>
+      </c>
+      <c r="R15" s="3">
         <v>25000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>28000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>30000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>29000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>8000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>9000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>25000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>200</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1501000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1688000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1680000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1664000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1544000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1654000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1669000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1590000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1478000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1062000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1006000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>940000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>805000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>903000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>896000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>858000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1092000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1146000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1105000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1004000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>896000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>164900</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E18" s="3">
         <v>71000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>104000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>107000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>70000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>49000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>66000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>59000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>50000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>41000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>38000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>62000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>31000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-234000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-161000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>63000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>26000</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,363 +1512,379 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>7000</v>
+        <v>-3000</v>
       </c>
       <c r="E20" s="3">
         <v>7000</v>
       </c>
       <c r="F20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="G20" s="3">
         <v>6000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>14000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>13000</v>
       </c>
       <c r="J20" s="3">
         <v>13000</v>
       </c>
       <c r="K20" s="3">
+        <v>13000</v>
+      </c>
+      <c r="L20" s="3">
         <v>11000</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>14000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>7000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>25000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>8000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2000</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E21" s="3">
         <v>155000</v>
-      </c>
-      <c r="E21" s="3">
-        <v>188000</v>
       </c>
       <c r="F21" s="3">
         <v>188000</v>
       </c>
       <c r="G21" s="3">
+        <v>188000</v>
+      </c>
+      <c r="H21" s="3">
         <v>149000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>142000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>152000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>148000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>80000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>98000</v>
-      </c>
-      <c r="M21" s="3">
-        <v>96000</v>
       </c>
       <c r="N21" s="3">
         <v>96000</v>
       </c>
       <c r="O21" s="3">
+        <v>96000</v>
+      </c>
+      <c r="P21" s="3">
         <v>51000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>60000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>120000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>112000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-161000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-67000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>48000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>90000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>53000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E22" s="3">
         <v>33000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>37000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>38000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>37000</v>
       </c>
       <c r="H22" s="3">
         <v>37000</v>
       </c>
       <c r="I22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="J22" s="3">
         <v>33000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>28000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>27000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>17000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>14000</v>
       </c>
       <c r="N22" s="3">
         <v>14000</v>
       </c>
       <c r="O22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="P22" s="3">
         <v>15000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>13000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>14000</v>
       </c>
       <c r="S22" s="3">
         <v>14000</v>
       </c>
       <c r="T22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="U22" s="3">
         <v>15000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>7000</v>
       </c>
       <c r="V22" s="3">
         <v>7000</v>
       </c>
       <c r="W22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="X22" s="3">
         <v>6000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>159600</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E23" s="3">
         <v>45000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>74000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>75000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>38000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>26000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>46000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>44000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-23000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>33000</v>
-      </c>
-      <c r="M23" s="3">
-        <v>30000</v>
       </c>
       <c r="N23" s="3">
         <v>30000</v>
       </c>
       <c r="O23" s="3">
+        <v>30000</v>
+      </c>
+      <c r="P23" s="3">
         <v>-14000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>55000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>24000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-245000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-151000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>14000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>57000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>22000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-159600</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="E24" s="3">
         <v>20000</v>
       </c>
       <c r="F24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="G24" s="3">
         <v>27000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>18000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-16000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>18000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-6000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>28000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-12000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-51000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>2000</v>
       </c>
       <c r="U24" s="3">
         <v>2000</v>
       </c>
       <c r="V24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W24" s="3">
         <v>4000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-159600</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E26" s="3">
         <v>25000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>54000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>48000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>26000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>22000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>28000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>30000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>15000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>27000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>36000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-194000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-153000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>12000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>53000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>21000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-159600</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-334000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-256000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>43000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>37000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>17000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-18000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-169000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>21000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-244000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>27000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>36000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-194000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-153000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>12000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>53000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>21000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-159600</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2398,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-7000</v>
+        <v>3000</v>
       </c>
       <c r="E32" s="3">
         <v>-7000</v>
       </c>
       <c r="F32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-6000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-14000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-13000</v>
       </c>
       <c r="J32" s="3">
         <v>-13000</v>
       </c>
       <c r="K32" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="L32" s="3">
         <v>-11000</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-7000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-25000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-8000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2000</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-334000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-256000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>43000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>37000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-18000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-169000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>21000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-244000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>27000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>36000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-194000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-153000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>12000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>53000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>21000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-159600</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-334000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-256000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>43000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>37000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-18000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-169000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>21000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-244000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>27000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>36000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-194000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-153000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>12000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>53000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>21000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-159600</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43159</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,62 +2831,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>247000</v>
+      </c>
+      <c r="E41" s="3">
         <v>479000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>461000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>368000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>363000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>605000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>395000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>330000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>315000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1188000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1128000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>686000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>745000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>515000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>467000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>377000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>436000</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2816,8 +2903,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,62 +2977,65 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1714000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1831000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1810000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1827000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1711000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1772000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1760000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1712000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1636000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>984000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>947000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>848000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>747000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>781000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>906000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>891000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>913000</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2958,62 +3051,65 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E44" s="3">
         <v>150000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>155000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>170000</v>
-      </c>
-      <c r="G44" s="3">
-        <v>163000</v>
       </c>
       <c r="H44" s="3">
         <v>163000</v>
       </c>
       <c r="I44" s="3">
+        <v>163000</v>
+      </c>
+      <c r="J44" s="3">
         <v>150000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>149000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>142000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>69000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>71000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>69000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>66000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>64000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>57000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>60000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>59000</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3029,62 +3125,65 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E45" s="3">
         <v>122000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>226000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>167000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>127000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>112000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>167000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>170000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>134000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>385000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>93000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>82000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>75000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>77000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>74000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>66000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>42000</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3100,62 +3199,65 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2232000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2582000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2652000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2532000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2364000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2652000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2472000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2361000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2227000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2626000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2239000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1685000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1633000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1437000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1504000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1394000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1450000</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3171,8 +3273,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3242,62 +3347,65 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>609000</v>
+      </c>
+      <c r="E48" s="3">
         <v>618000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>604000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>639000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>621000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>629000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>608000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>614000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>628000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>427000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>439000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>453000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>459000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>462000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>452000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>467000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>500000</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3313,62 +3421,65 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4020000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4091000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4028000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4147000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4139000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4166000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4010000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4254000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4492000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1988000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1996000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1991000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2008000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2047000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1772000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1799000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1836000</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3384,8 +3495,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,62 +3643,65 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>331000</v>
+      </c>
+      <c r="E52" s="3">
         <v>299000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>665000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>656000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>642000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>644000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>851000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>825000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>795000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>118000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>109000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>114000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>118000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>119000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>98000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>110000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>100000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,62 +3791,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7192000</v>
+      </c>
+      <c r="E54" s="3">
         <v>7590000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7949000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7974000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7766000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8091000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7941000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8054000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8142000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5159000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4783000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4243000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4218000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4065000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3826000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3770000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3886000</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,8 +3865,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,62 +3923,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>382000</v>
+      </c>
+      <c r="E57" s="3">
         <v>472000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>431000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>473000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>442000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>490000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>469000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>448000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>391000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>236000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>205000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>180000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>167000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>150000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>142000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>155000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>152000</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,62 +3995,65 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>328000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>79000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>78000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>212000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>28000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>29000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>42000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>63000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>49000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>44000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>45000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>244000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3935,62 +4069,65 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1092000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1324000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1140000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1099000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1029000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1219000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1043000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>998000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>971000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>603000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>558000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>508000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>551000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>642000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>648000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>621000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>523000</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4006,62 +4143,65 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1654000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1807000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1899000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1651000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1549000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1921000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1523000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1453000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1367000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>867000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>792000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>730000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>781000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>841000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>834000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>821000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>919000</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4077,62 +4217,65 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2797000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2330000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2512000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2758000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2743000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2595000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2791000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2823000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2819000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1845000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1548000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1538000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1475000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1493000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1248000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1254000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1260000</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4148,62 +4291,65 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>440000</v>
+      </c>
+      <c r="E62" s="3">
         <v>585000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>509000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>521000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>512000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>651000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>680000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>825000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>881000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>124000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>146000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>147000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>171000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>173000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>146000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>130000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>182000</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,62 +4587,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4891000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4722000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4920000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4930000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4804000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5167000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4994000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5101000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5067000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2836000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2486000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2415000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2427000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2507000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2228000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2205000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2361000</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,8 +4661,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,13 +4837,16 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>797000</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3">
         <v>797000</v>
@@ -4702,7 +4870,7 @@
         <v>797000</v>
       </c>
       <c r="L70" s="3">
-        <v>0</v>
+        <v>797000</v>
       </c>
       <c r="M70" s="3">
         <v>0</v>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,62 +4985,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-36000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-90000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-138000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-164000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-186000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-214000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-255000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-237000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-252000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-271000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-292000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-284000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-262000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-289000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-325000</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4879,14 +5053,17 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X72" s="3">
-        <v>0</v>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,62 +5281,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2301000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2071000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2232000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2247000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2165000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2127000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2150000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2156000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2278000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2323000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2297000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1828000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1791000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1558000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1598000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1565000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1525000</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5169,8 +5355,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43159</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-334000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-256000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>43000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>37000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-18000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-169000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>21000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-244000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>27000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>36000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-194000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-153000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>12000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>53000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>21000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-159600</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,79 +5612,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>77000</v>
+        <v>69000</v>
       </c>
       <c r="E83" s="3">
         <v>77000</v>
       </c>
       <c r="F83" s="3">
+        <v>77000</v>
+      </c>
+      <c r="G83" s="3">
         <v>75000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>74000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>79000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>73000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>76000</v>
       </c>
       <c r="K83" s="3">
         <v>76000</v>
       </c>
       <c r="L83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="M83" s="3">
         <v>48000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>52000</v>
       </c>
       <c r="N83" s="3">
         <v>52000</v>
       </c>
       <c r="O83" s="3">
+        <v>52000</v>
+      </c>
+      <c r="P83" s="3">
         <v>50000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>67000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>52000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>74000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>70000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>69000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>27000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>26000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>25000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E89" s="3">
         <v>297000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>144000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>74000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>188000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>146000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>54000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-118000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>114000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>49000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-13000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>32000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>167000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>97000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>177000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>55000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>150000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>92000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>28000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>25000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>40000</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,8 +6158,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5947,70 +6168,73 @@
         <v>-22000</v>
       </c>
       <c r="E91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-18000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-21000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-19000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-26000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-22000</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-12000</v>
       </c>
       <c r="L91" s="3">
         <v>-12000</v>
       </c>
       <c r="M91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="N91" s="3">
         <v>-9000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-18000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6000</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-11000</v>
       </c>
       <c r="T91" s="3">
         <v>-11000</v>
       </c>
       <c r="U91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="V91" s="3">
         <v>-13000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-18000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-22000</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6378,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-26000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-55000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>30000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-28000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2884000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-40000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-46000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-12000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-23000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-323000</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-1000</v>
       </c>
       <c r="R94" s="3">
         <v>-1000</v>
       </c>
       <c r="S94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="T94" s="3">
         <v>-15000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1728000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-19000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-22000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>18600</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6482,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,217 +6776,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-213000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-279000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-21000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-16000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-216000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-17000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-45000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-13000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1831000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>288000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>442000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-36000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>223000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>200000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-235000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>139000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1398000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>25000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-19000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-16000</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E101" s="3">
         <v>7000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>2000</v>
       </c>
       <c r="G101" s="3">
         <v>2000</v>
       </c>
       <c r="H101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I101" s="3">
         <v>8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-7000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
+      <c r="X101" s="3">
+        <v>0</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-232000</v>
+      </c>
+      <c r="E102" s="3">
         <v>18000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>92000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-242000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>209000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>65000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>15000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1173000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>361000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>441000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-59000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>233000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>48000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>90000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-59000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>180000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-181000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>107000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-10000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-13000</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>APG</t>
   </si>
@@ -656,340 +656,353 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43159</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1730000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1601000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1759000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1784000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1771000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1614000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1703000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1735000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1649000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1471000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1112000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1047000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>978000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>803000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>882000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>958000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>889000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>858000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>985000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1118000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1067000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>922000</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1186000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1109000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1251000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1273000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1275000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1189000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1237000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1293000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1212000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1095000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>838000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>795000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>746000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>622000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>684000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>736000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>692000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>696000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>787000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>885000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>859000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>759000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>400</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>544000</v>
+      </c>
+      <c r="E10" s="3">
         <v>492000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>508000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>511000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>496000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>425000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>466000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>442000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>437000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>376000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>274000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>252000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>232000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>181000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>198000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>222000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>197000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>162000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>198000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>233000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>208000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>163000</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,8 +1029,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1090,8 +1104,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,117 +1181,123 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="E14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F14" s="3">
         <v>13000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>37000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>12000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>24000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>9000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-11000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-4000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>208000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>12000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>50000</v>
+        <v>52000</v>
       </c>
       <c r="E15" s="3">
         <v>50000</v>
       </c>
       <c r="F15" s="3">
+        <v>50000</v>
+      </c>
+      <c r="G15" s="3">
         <v>49000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>50000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>48000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>54000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>36000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>53000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>54000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>32000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>30000</v>
       </c>
       <c r="O15" s="3">
         <v>30000</v>
@@ -1286,34 +1309,37 @@
         <v>30000</v>
       </c>
       <c r="R15" s="3">
+        <v>30000</v>
+      </c>
+      <c r="S15" s="3">
         <v>25000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>28000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>30000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>29000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>8000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>9000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>25000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>200</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1363,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1604000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1501000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1688000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1680000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1664000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1544000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1654000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1669000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1590000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1478000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1062000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1006000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>940000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>805000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>903000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>896000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>858000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1092000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1146000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1105000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1004000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>896000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>164900</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>126000</v>
+      </c>
+      <c r="E18" s="3">
         <v>100000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>71000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>104000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>107000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>70000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>49000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>66000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>59000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>50000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>41000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>38000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-21000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>62000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>31000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-234000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-161000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>13000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>63000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>26000</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,378 +1546,394 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>7000</v>
       </c>
       <c r="F20" s="3">
         <v>7000</v>
       </c>
       <c r="G20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H20" s="3">
         <v>6000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>14000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>13000</v>
       </c>
       <c r="K20" s="3">
         <v>13000</v>
       </c>
       <c r="L20" s="3">
+        <v>13000</v>
+      </c>
+      <c r="M20" s="3">
         <v>11000</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>14000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>7000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>25000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>8000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2000</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>199000</v>
+      </c>
+      <c r="E21" s="3">
         <v>166000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>155000</v>
-      </c>
-      <c r="F21" s="3">
-        <v>188000</v>
       </c>
       <c r="G21" s="3">
         <v>188000</v>
       </c>
       <c r="H21" s="3">
+        <v>188000</v>
+      </c>
+      <c r="I21" s="3">
         <v>149000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>142000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>152000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>148000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>80000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>98000</v>
-      </c>
-      <c r="N21" s="3">
-        <v>96000</v>
       </c>
       <c r="O21" s="3">
         <v>96000</v>
       </c>
       <c r="P21" s="3">
+        <v>96000</v>
+      </c>
+      <c r="Q21" s="3">
         <v>51000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>60000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>120000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>112000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-161000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-67000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>48000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>90000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>53000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E22" s="3">
         <v>34000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>33000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>37000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>38000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>37000</v>
       </c>
       <c r="I22" s="3">
         <v>37000</v>
       </c>
       <c r="J22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="K22" s="3">
         <v>33000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>28000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>27000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>17000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>14000</v>
       </c>
       <c r="O22" s="3">
         <v>14000</v>
       </c>
       <c r="P22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>15000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>11000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>13000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>14000</v>
       </c>
       <c r="T22" s="3">
         <v>14000</v>
       </c>
       <c r="U22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="V22" s="3">
         <v>15000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>7000</v>
       </c>
       <c r="W22" s="3">
         <v>7000</v>
       </c>
       <c r="X22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>6000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>159600</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E23" s="3">
         <v>63000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>45000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>74000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>75000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>38000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>26000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>46000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>44000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-23000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>33000</v>
-      </c>
-      <c r="N23" s="3">
-        <v>30000</v>
       </c>
       <c r="O23" s="3">
         <v>30000</v>
       </c>
       <c r="P23" s="3">
+        <v>30000</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-18000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>55000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>24000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-245000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-151000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>14000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>57000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>22000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-159600</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E24" s="3">
         <v>18000</v>
-      </c>
-      <c r="E24" s="3">
-        <v>20000</v>
       </c>
       <c r="F24" s="3">
         <v>20000</v>
       </c>
       <c r="G24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="H24" s="3">
         <v>27000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>18000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-16000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>18000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>28000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-12000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-51000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>2000</v>
       </c>
       <c r="V24" s="3">
         <v>2000</v>
       </c>
       <c r="W24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X24" s="3">
         <v>4000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-159600</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2006,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E26" s="3">
         <v>45000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>25000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>54000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>48000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>26000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>22000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>28000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>30000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>15000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>21000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-22000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>27000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>36000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-194000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-153000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>12000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>53000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>21000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-159600</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-334000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-256000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>43000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>37000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>17000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-18000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-169000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>21000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-244000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>27000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>36000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-194000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-153000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>12000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>53000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>21000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-159600</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,156 +2468,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>3000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-7000</v>
       </c>
       <c r="F32" s="3">
         <v>-7000</v>
       </c>
       <c r="G32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-6000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-14000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-13000</v>
       </c>
       <c r="K32" s="3">
         <v>-13000</v>
       </c>
       <c r="L32" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="M32" s="3">
         <v>-11000</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-14000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-7000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-25000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-8000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-334000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-256000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>43000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>37000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-18000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-169000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>21000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-244000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>27000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>36000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-194000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-153000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>12000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>53000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>21000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-159600</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2699,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-334000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-256000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>43000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>37000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-18000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-169000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>21000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-244000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>27000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>36000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-194000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-153000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>12000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>53000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>21000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-159600</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43159</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,65 +2918,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>324000</v>
+      </c>
+      <c r="E41" s="3">
         <v>247000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>479000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>461000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>368000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>363000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>605000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>395000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>330000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>315000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1188000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1128000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>686000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>745000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>515000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>467000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>377000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>436000</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2906,8 +2993,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2980,65 +3070,68 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1823000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1714000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1831000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1810000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1827000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1711000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1772000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1760000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1712000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1636000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>984000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>947000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>848000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>747000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>781000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>906000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>891000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>913000</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3054,65 +3147,68 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E44" s="3">
         <v>148000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>150000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>155000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>170000</v>
-      </c>
-      <c r="H44" s="3">
-        <v>163000</v>
       </c>
       <c r="I44" s="3">
         <v>163000</v>
       </c>
       <c r="J44" s="3">
+        <v>163000</v>
+      </c>
+      <c r="K44" s="3">
         <v>150000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>149000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>142000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>69000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>71000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>69000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>66000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>64000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>57000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>60000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>59000</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3128,65 +3224,68 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>152000</v>
+      </c>
+      <c r="E45" s="3">
         <v>123000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>122000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>226000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>167000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>127000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>112000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>167000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>170000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>134000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>385000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>93000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>82000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>75000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>77000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>74000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>66000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>42000</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3202,65 +3301,68 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2454000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2232000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2582000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2652000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2532000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2364000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2652000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2472000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2361000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2227000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2626000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2239000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1685000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1633000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1437000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1504000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1394000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1450000</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3276,8 +3378,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3350,65 +3455,68 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>634000</v>
+      </c>
+      <c r="E48" s="3">
         <v>609000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>618000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>604000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>639000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>621000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>629000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>608000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>614000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>628000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>427000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>439000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>453000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>459000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>462000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>452000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>467000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>500000</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3424,65 +3532,68 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4598000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4020000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4091000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4028000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4147000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4139000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4166000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4010000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4254000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4492000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1988000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1996000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1991000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2008000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2047000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1772000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1799000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1836000</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3498,8 +3609,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,65 +3763,68 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>275000</v>
+      </c>
+      <c r="E52" s="3">
         <v>331000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>299000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>665000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>656000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>642000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>644000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>851000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>825000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>795000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>118000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>109000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>114000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>118000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>119000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>98000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>110000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>100000</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3720,8 +3840,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,65 +3917,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7961000</v>
+      </c>
+      <c r="E54" s="3">
         <v>7192000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7590000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7949000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7974000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7766000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8091000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7941000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8054000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8142000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5159000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4783000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4243000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4218000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4065000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3826000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3770000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3886000</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3868,8 +3994,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,65 +4054,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>424000</v>
+      </c>
+      <c r="E57" s="3">
         <v>382000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>472000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>431000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>473000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>442000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>490000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>469000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>448000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>391000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>236000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>205000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>180000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>167000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>150000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>142000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>155000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>152000</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,65 +4129,68 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E58" s="3">
         <v>180000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>328000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>79000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>78000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>212000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>28000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>29000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>42000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>63000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>49000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>44000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>45000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>244000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4072,65 +4206,68 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1152000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1092000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1324000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1140000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1099000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1029000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1219000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1043000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>998000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>971000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>603000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>558000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>508000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>551000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>642000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>648000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>621000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>523000</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4146,65 +4283,68 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1662000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1654000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1807000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1899000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1651000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1549000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1921000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1523000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1453000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1367000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>867000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>792000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>730000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>781000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>841000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>834000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>821000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>919000</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4220,65 +4360,68 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3029000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2797000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2330000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2512000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2758000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2743000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2595000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2791000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2823000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2819000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1845000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1548000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1538000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1475000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1493000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1248000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1254000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1260000</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4294,65 +4437,68 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>435000</v>
+      </c>
+      <c r="E62" s="3">
         <v>440000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>585000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>509000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>521000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>512000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>651000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>680000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>825000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>881000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>124000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>146000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>147000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>171000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>173000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>146000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>130000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>182000</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4368,8 +4514,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,65 +4745,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5126000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4891000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4722000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4920000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4930000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4804000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5167000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4994000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5101000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5067000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2836000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2486000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2415000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2427000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2507000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2228000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2205000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2361000</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4664,8 +4822,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4849,7 +5017,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>797000</v>
+        <v>0</v>
       </c>
       <c r="F70" s="3">
         <v>797000</v>
@@ -4873,7 +5041,7 @@
         <v>797000</v>
       </c>
       <c r="M70" s="3">
-        <v>0</v>
+        <v>797000</v>
       </c>
       <c r="N70" s="3">
         <v>0</v>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,65 +5159,68 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E72" s="3">
         <v>10000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-11000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-36000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-90000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-138000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-164000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-186000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-214000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-255000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-237000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-252000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-271000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-292000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-284000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-262000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-289000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-325000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5056,14 +5230,17 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y72" s="3">
-        <v>0</v>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,65 +5467,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2835000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2301000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2071000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2232000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2247000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2165000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2127000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2150000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2156000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2278000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2323000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2297000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1828000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1791000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1558000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1598000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1565000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1525000</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,8 +5544,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5621,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43159</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-334000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-256000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>43000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>37000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-18000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-169000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>21000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-244000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>27000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>36000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-194000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-153000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>12000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>53000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>21000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-159600</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,82 +5811,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E83" s="3">
         <v>69000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>77000</v>
       </c>
       <c r="F83" s="3">
         <v>77000</v>
       </c>
       <c r="G83" s="3">
+        <v>77000</v>
+      </c>
+      <c r="H83" s="3">
         <v>75000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>74000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>79000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>73000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>76000</v>
       </c>
       <c r="L83" s="3">
         <v>76000</v>
       </c>
       <c r="M83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="N83" s="3">
         <v>48000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>52000</v>
       </c>
       <c r="O83" s="3">
         <v>52000</v>
       </c>
       <c r="P83" s="3">
+        <v>52000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>50000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>67000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>52000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>74000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>70000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>69000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>27000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>26000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>25000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6271,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E89" s="3">
         <v>7000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>297000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>144000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>74000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>188000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>146000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>54000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-118000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>114000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>49000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-13000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>32000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>167000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>97000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>177000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>55000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>150000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>92000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>28000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>25000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>40000</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,8 +6379,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6171,70 +6392,73 @@
         <v>-22000</v>
       </c>
       <c r="F91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="G91" s="3">
         <v>-18000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-25000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-21000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-19000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-26000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-22000</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-12000</v>
       </c>
       <c r="M91" s="3">
         <v>-12000</v>
       </c>
       <c r="N91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="O91" s="3">
         <v>-9000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-14000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6000</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-11000</v>
       </c>
       <c r="U91" s="3">
         <v>-11000</v>
       </c>
       <c r="V91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="W91" s="3">
         <v>-13000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-18000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,82 +6608,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-601000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-22000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-26000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-55000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-27000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>30000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-28000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2884000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-40000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-46000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-323000</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-1000</v>
       </c>
       <c r="S94" s="3">
         <v>-1000</v>
       </c>
       <c r="T94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U94" s="3">
         <v>-15000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1728000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-10000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-19000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>18600</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6716,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,226 +7022,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>570000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-213000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-279000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-21000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-16000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-216000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-17000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-45000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1831000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>288000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>442000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-36000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>223000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-235000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>139000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1398000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>25000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-19000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>7000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>2000</v>
       </c>
       <c r="H101" s="3">
         <v>2000</v>
       </c>
       <c r="I101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J101" s="3">
         <v>8000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-7000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
+      <c r="Y101" s="3">
+        <v>0</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-232000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>18000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>92000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-242000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>209000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>65000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1173000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>361000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>441000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-59000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>233000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>48000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>90000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-59000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>180000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-181000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>107000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-10000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>APG</t>
   </si>
@@ -656,353 +656,366 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43159</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1826000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1730000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1601000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1759000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1784000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1771000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1614000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1703000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1735000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1649000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1471000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1112000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1047000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>978000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>803000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>882000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>958000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>889000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>858000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>985000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1118000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1067000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>922000</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1259000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1186000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1109000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1251000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1273000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1275000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1189000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1237000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1293000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1212000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1095000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>838000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>795000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>746000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>622000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>684000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>736000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>692000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>696000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>787000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>885000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>859000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>759000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>400</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>567000</v>
+      </c>
+      <c r="E10" s="3">
         <v>544000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>492000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>508000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>511000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>496000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>425000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>466000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>442000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>437000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>376000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>274000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>252000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>232000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>181000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>198000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>222000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>197000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>162000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>198000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>233000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>208000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>163000</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,8 +1043,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1107,8 +1121,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,123 +1201,129 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>15000</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
-        <v>5000</v>
+        <v>-12000</v>
       </c>
       <c r="F14" s="3">
-        <v>13000</v>
+        <v>19000</v>
       </c>
       <c r="G14" s="3">
-        <v>37000</v>
+        <v>4000</v>
       </c>
       <c r="H14" s="3">
-        <v>4000</v>
-      </c>
-      <c r="I14" s="3">
+        <v>22000</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>3000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>12000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>24000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>9000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-11000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-4000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>208000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>12000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E15" s="3">
         <v>52000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>50000</v>
       </c>
       <c r="F15" s="3">
         <v>50000</v>
       </c>
       <c r="G15" s="3">
+        <v>-147000</v>
+      </c>
+      <c r="H15" s="3">
         <v>49000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>50000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>48000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>54000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>36000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>53000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>54000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>32000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>30000</v>
       </c>
       <c r="P15" s="3">
         <v>30000</v>
@@ -1312,34 +1335,37 @@
         <v>30000</v>
       </c>
       <c r="S15" s="3">
+        <v>30000</v>
+      </c>
+      <c r="T15" s="3">
         <v>25000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>28000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>30000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>29000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>8000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>9000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>25000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>200</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1390,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1604000</v>
+        <v>1689000</v>
       </c>
       <c r="E17" s="3">
+        <v>1606000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1501000</v>
       </c>
-      <c r="F17" s="3">
-        <v>1688000</v>
-      </c>
       <c r="G17" s="3">
-        <v>1680000</v>
+        <v>1681000</v>
       </c>
       <c r="H17" s="3">
-        <v>1664000</v>
+        <v>1677000</v>
       </c>
       <c r="I17" s="3">
-        <v>1544000</v>
+        <v>1661000</v>
       </c>
       <c r="J17" s="3">
+        <v>1538000</v>
+      </c>
+      <c r="K17" s="3">
         <v>1654000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1669000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1590000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1478000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1062000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1006000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>940000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>805000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>903000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>896000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>858000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1092000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1146000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1105000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1004000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>896000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>164900</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>126000</v>
+        <v>137000</v>
       </c>
       <c r="E18" s="3">
+        <v>124000</v>
+      </c>
+      <c r="F18" s="3">
         <v>100000</v>
       </c>
-      <c r="F18" s="3">
-        <v>71000</v>
-      </c>
       <c r="G18" s="3">
-        <v>104000</v>
+        <v>78000</v>
       </c>
       <c r="H18" s="3">
         <v>107000</v>
       </c>
       <c r="I18" s="3">
-        <v>70000</v>
+        <v>110000</v>
       </c>
       <c r="J18" s="3">
+        <v>76000</v>
+      </c>
+      <c r="K18" s="3">
         <v>49000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>66000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>59000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>50000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>41000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>38000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-21000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>62000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>31000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-234000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-161000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>63000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>26000</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,393 +1580,409 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-2000</v>
       </c>
-      <c r="E20" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>7000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>7000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>6000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>5000</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>14000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>13000</v>
       </c>
       <c r="L20" s="3">
         <v>13000</v>
       </c>
       <c r="M20" s="3">
+        <v>13000</v>
+      </c>
+      <c r="N20" s="3">
         <v>11000</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>3000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>14000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>7000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>25000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>8000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2000</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>199000</v>
+        <v>166000</v>
       </c>
       <c r="E21" s="3">
+        <v>182000</v>
+      </c>
+      <c r="F21" s="3">
         <v>166000</v>
       </c>
-      <c r="F21" s="3">
-        <v>155000</v>
-      </c>
       <c r="G21" s="3">
-        <v>188000</v>
+        <v>-66000</v>
       </c>
       <c r="H21" s="3">
-        <v>188000</v>
+        <v>182000</v>
       </c>
       <c r="I21" s="3">
-        <v>149000</v>
+        <v>147000</v>
       </c>
       <c r="J21" s="3">
+        <v>126000</v>
+      </c>
+      <c r="K21" s="3">
         <v>142000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>152000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>148000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>80000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>98000</v>
-      </c>
-      <c r="O21" s="3">
-        <v>96000</v>
       </c>
       <c r="P21" s="3">
         <v>96000</v>
       </c>
       <c r="Q21" s="3">
+        <v>96000</v>
+      </c>
+      <c r="R21" s="3">
         <v>51000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>60000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>120000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>112000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-161000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-67000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>48000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>90000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>53000</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E22" s="3">
         <v>35000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>34000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>33000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>37000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>38000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>37000</v>
       </c>
       <c r="J22" s="3">
         <v>37000</v>
       </c>
       <c r="K22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="L22" s="3">
         <v>33000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>28000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>27000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>17000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>14000</v>
       </c>
       <c r="P22" s="3">
         <v>14000</v>
       </c>
       <c r="Q22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="R22" s="3">
         <v>15000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>13000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>14000</v>
       </c>
       <c r="U22" s="3">
         <v>14000</v>
       </c>
       <c r="V22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="W22" s="3">
         <v>15000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>7000</v>
       </c>
       <c r="X22" s="3">
         <v>7000</v>
       </c>
       <c r="Y22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>6000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>159600</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E23" s="3">
         <v>89000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>63000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>45000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>74000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>75000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>38000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>26000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>46000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>44000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-23000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>33000</v>
-      </c>
-      <c r="O23" s="3">
-        <v>30000</v>
       </c>
       <c r="P23" s="3">
         <v>30000</v>
       </c>
       <c r="Q23" s="3">
+        <v>30000</v>
+      </c>
+      <c r="R23" s="3">
         <v>-14000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-18000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>55000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>24000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-245000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-151000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>14000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>57000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>22000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-159600</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E24" s="3">
         <v>20000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>18000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>20000</v>
       </c>
       <c r="G24" s="3">
         <v>20000</v>
       </c>
       <c r="H24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="I24" s="3">
         <v>27000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>18000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-16000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>18000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-6000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>28000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-12000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-51000</v>
-      </c>
-      <c r="V24" s="3">
-        <v>2000</v>
       </c>
       <c r="W24" s="3">
         <v>2000</v>
       </c>
       <c r="X24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y24" s="3">
         <v>4000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-159600</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,8 +2058,11 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2018,153 +2070,159 @@
         <v>69000</v>
       </c>
       <c r="E26" s="3">
+        <v>69000</v>
+      </c>
+      <c r="F26" s="3">
         <v>45000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>25000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>54000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>48000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>26000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>22000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>28000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>30000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>15000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>21000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-22000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>27000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>36000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-194000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-153000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>12000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>53000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>21000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-159600</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E27" s="3">
         <v>69000</v>
       </c>
-      <c r="E27" s="3">
-        <v>-334000</v>
-      </c>
       <c r="F27" s="3">
-        <v>-256000</v>
+        <v>-327000</v>
       </c>
       <c r="G27" s="3">
-        <v>43000</v>
+        <v>-236000</v>
       </c>
       <c r="H27" s="3">
-        <v>37000</v>
+        <v>35000</v>
       </c>
       <c r="I27" s="3">
-        <v>15000</v>
+        <v>28000</v>
       </c>
       <c r="J27" s="3">
+        <v>12000</v>
+      </c>
+      <c r="K27" s="3">
         <v>11000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>17000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-169000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>21000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-244000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>27000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>36000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-194000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-153000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>12000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>53000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>21000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-159600</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2298,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2378,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2458,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,85 +2538,91 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F32" s="3">
+        <v>16000</v>
+      </c>
+      <c r="G32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H32" s="3">
+        <v>26000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="J32" s="3">
         <v>2000</v>
       </c>
-      <c r="E32" s="3">
-        <v>3000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-14000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-13000</v>
       </c>
       <c r="L32" s="3">
         <v>-13000</v>
       </c>
       <c r="M32" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="N32" s="3">
         <v>-11000</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-3000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-14000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-7000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-25000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-8000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2557,76 +2630,79 @@
         <v>69000</v>
       </c>
       <c r="E33" s="3">
-        <v>-334000</v>
+        <v>69000</v>
       </c>
       <c r="F33" s="3">
-        <v>-256000</v>
+        <v>45000</v>
       </c>
       <c r="G33" s="3">
-        <v>43000</v>
+        <v>25000</v>
       </c>
       <c r="H33" s="3">
-        <v>37000</v>
+        <v>54000</v>
       </c>
       <c r="I33" s="3">
-        <v>15000</v>
+        <v>48000</v>
       </c>
       <c r="J33" s="3">
+        <v>26000</v>
+      </c>
+      <c r="K33" s="3">
         <v>11000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-18000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-169000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>21000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-244000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>27000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>36000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-194000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-153000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>12000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>53000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>21000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-159600</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,8 +2778,11 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2711,158 +2790,164 @@
         <v>69000</v>
       </c>
       <c r="E35" s="3">
-        <v>-334000</v>
+        <v>69000</v>
       </c>
       <c r="F35" s="3">
-        <v>-256000</v>
+        <v>45000</v>
       </c>
       <c r="G35" s="3">
-        <v>43000</v>
+        <v>25000</v>
       </c>
       <c r="H35" s="3">
-        <v>37000</v>
+        <v>54000</v>
       </c>
       <c r="I35" s="3">
-        <v>15000</v>
+        <v>48000</v>
       </c>
       <c r="J35" s="3">
+        <v>26000</v>
+      </c>
+      <c r="K35" s="3">
         <v>11000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-18000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-169000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>21000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-244000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>27000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>36000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-194000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-153000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>12000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>53000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>21000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-159600</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43159</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2975,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,68 +3005,69 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>487000</v>
+      </c>
+      <c r="E41" s="3">
         <v>324000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>247000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>479000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>461000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>368000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>363000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>605000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>395000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>330000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>315000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1188000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1128000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>686000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>745000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>515000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>467000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>377000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>436000</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,8 +3083,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3073,68 +3163,71 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1897000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1823000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1714000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1831000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1810000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1827000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1711000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1772000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1760000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1712000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1636000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>984000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>947000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>848000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>747000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>781000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>906000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>891000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>913000</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3150,8 +3243,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3159,59 +3255,59 @@
         <v>155000</v>
       </c>
       <c r="E44" s="3">
+        <v>155000</v>
+      </c>
+      <c r="F44" s="3">
         <v>148000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>150000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>155000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>170000</v>
-      </c>
-      <c r="I44" s="3">
-        <v>163000</v>
       </c>
       <c r="J44" s="3">
         <v>163000</v>
       </c>
       <c r="K44" s="3">
+        <v>163000</v>
+      </c>
+      <c r="L44" s="3">
         <v>150000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>149000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>142000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>69000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>71000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>69000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>66000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>64000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>57000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>60000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>59000</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3227,68 +3323,71 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>152000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>123000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>122000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>226000</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
+        <v>112000</v>
+      </c>
+      <c r="L45" s="3">
         <v>167000</v>
       </c>
-      <c r="I45" s="3">
-        <v>127000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>112000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>167000</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>170000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>134000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>385000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>93000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>82000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>75000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>77000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>74000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>66000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>42000</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3304,68 +3403,71 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2691000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2454000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2232000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2582000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2652000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2532000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2364000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2652000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2472000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2361000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2227000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2626000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2239000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1685000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1633000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1437000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1504000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1394000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1450000</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3381,31 +3483,34 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3458,68 +3563,71 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>651000</v>
+      </c>
+      <c r="E48" s="3">
         <v>634000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>609000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>618000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>604000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>639000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>621000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>629000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>608000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>614000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>628000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>427000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>439000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>453000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>459000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>462000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>452000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>467000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>500000</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3535,68 +3643,71 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4663000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4598000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4020000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4091000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4028000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4147000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4139000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4166000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4010000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4254000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4492000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1988000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1996000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1991000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2008000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2047000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1772000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1799000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1836000</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3612,8 +3723,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3803,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,68 +3883,71 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>275000</v>
+        <v>166000</v>
       </c>
       <c r="E52" s="3">
-        <v>331000</v>
+        <v>196000</v>
       </c>
       <c r="F52" s="3">
-        <v>299000</v>
+        <v>189000</v>
       </c>
       <c r="G52" s="3">
-        <v>665000</v>
+        <v>175000</v>
       </c>
       <c r="H52" s="3">
-        <v>656000</v>
+        <v>516000</v>
       </c>
       <c r="I52" s="3">
-        <v>642000</v>
+        <v>519000</v>
       </c>
       <c r="J52" s="3">
+        <v>523000</v>
+      </c>
+      <c r="K52" s="3">
         <v>644000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>851000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>825000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>795000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>118000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>109000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>114000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>118000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>119000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>98000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>110000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>100000</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3843,8 +3963,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,68 +4043,71 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8245000</v>
+      </c>
+      <c r="E54" s="3">
         <v>7961000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7192000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7590000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7949000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7974000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7766000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8091000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7941000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8054000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8142000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5159000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4783000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4243000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4218000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4065000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3826000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3770000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3886000</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,8 +4123,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4155,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,68 +4185,69 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>454000</v>
+      </c>
+      <c r="E57" s="3">
         <v>424000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>382000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>472000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>431000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>473000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>442000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>490000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>469000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>448000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>391000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>236000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>205000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>180000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>167000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>150000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>142000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>155000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>152000</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4132,68 +4263,71 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E58" s="3">
         <v>86000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>180000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
+        <v>80000</v>
+      </c>
+      <c r="H58" s="3">
+        <v>328000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>79000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>78000</v>
+      </c>
+      <c r="K58" s="3">
+        <v>212000</v>
+      </c>
+      <c r="L58" s="3">
         <v>11000</v>
       </c>
-      <c r="G58" s="3">
-        <v>328000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>79000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>78000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>212000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>11000</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>28000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>29000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>42000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>63000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>49000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>44000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>45000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>244000</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4209,68 +4343,71 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1152000</v>
+        <v>608000</v>
       </c>
       <c r="E59" s="3">
-        <v>1092000</v>
+        <v>590000</v>
       </c>
       <c r="F59" s="3">
-        <v>1324000</v>
+        <v>587000</v>
       </c>
       <c r="G59" s="3">
-        <v>1140000</v>
+        <v>548000</v>
       </c>
       <c r="H59" s="3">
-        <v>1099000</v>
+        <v>515000</v>
       </c>
       <c r="I59" s="3">
-        <v>1029000</v>
+        <v>523000</v>
       </c>
       <c r="J59" s="3">
+        <v>518000</v>
+      </c>
+      <c r="K59" s="3">
         <v>1219000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1043000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>998000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>971000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>603000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>558000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>508000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>551000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>642000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>648000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>621000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>523000</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4286,68 +4423,71 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1781000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1662000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1654000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1807000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1899000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1651000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1549000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1921000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1523000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1453000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1367000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>867000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>792000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>730000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>781000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>841000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>834000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>821000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>919000</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4363,68 +4503,71 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3044000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3029000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2797000</v>
       </c>
-      <c r="F61" s="3">
-        <v>2330000</v>
-      </c>
       <c r="G61" s="3">
+        <v>2494000</v>
+      </c>
+      <c r="H61" s="3">
         <v>2512000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2758000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2743000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2595000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2791000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2823000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2819000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1845000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1548000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1538000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1475000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1493000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1248000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1254000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1260000</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4440,68 +4583,71 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>435000</v>
+        <v>153000</v>
       </c>
       <c r="E62" s="3">
-        <v>440000</v>
+        <v>149000</v>
       </c>
       <c r="F62" s="3">
-        <v>585000</v>
+        <v>156000</v>
       </c>
       <c r="G62" s="3">
-        <v>509000</v>
+        <v>90000</v>
       </c>
       <c r="H62" s="3">
-        <v>521000</v>
+        <v>132000</v>
       </c>
       <c r="I62" s="3">
-        <v>512000</v>
+        <v>132000</v>
       </c>
       <c r="J62" s="3">
+        <v>130000</v>
+      </c>
+      <c r="K62" s="3">
         <v>651000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>680000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>825000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>881000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>124000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>146000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>147000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>171000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>173000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>146000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>130000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>182000</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4517,8 +4663,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4743,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4823,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,68 +4903,71 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5278000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5126000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4891000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4722000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4920000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4930000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4804000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5167000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4994000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5101000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5067000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2836000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2486000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2415000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2427000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2507000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2228000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2205000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2361000</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4825,8 +4983,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5015,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5093,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5173,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5020,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>797000</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3">
         <v>797000</v>
@@ -5044,7 +5212,7 @@
         <v>797000</v>
       </c>
       <c r="N70" s="3">
-        <v>0</v>
+        <v>797000</v>
       </c>
       <c r="O70" s="3">
         <v>0</v>
@@ -5085,8 +5253,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,68 +5333,71 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E72" s="3">
         <v>79000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-36000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-90000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-138000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-164000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-186000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-214000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-255000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-237000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-252000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-271000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-292000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-284000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-262000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-289000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-325000</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5233,14 +5407,17 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z72" s="3">
-        <v>0</v>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5493,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5573,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,68 +5653,71 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2967000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2835000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2301000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2071000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2232000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2247000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2165000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2127000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2150000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2156000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2278000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2323000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2297000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1828000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1791000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1558000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1598000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1565000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1525000</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5547,8 +5733,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,90 +5813,96 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43159</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5715,76 +5910,79 @@
         <v>69000</v>
       </c>
       <c r="E81" s="3">
-        <v>-334000</v>
+        <v>69000</v>
       </c>
       <c r="F81" s="3">
-        <v>-256000</v>
+        <v>45000</v>
       </c>
       <c r="G81" s="3">
-        <v>43000</v>
+        <v>25000</v>
       </c>
       <c r="H81" s="3">
-        <v>37000</v>
+        <v>54000</v>
       </c>
       <c r="I81" s="3">
-        <v>15000</v>
+        <v>48000</v>
       </c>
       <c r="J81" s="3">
+        <v>26000</v>
+      </c>
+      <c r="K81" s="3">
         <v>11000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-18000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-169000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>21000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-244000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>27000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>36000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-194000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-153000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>12000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>53000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>21000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-159600</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,85 +6010,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>75000</v>
+        <v>21000</v>
       </c>
       <c r="E83" s="3">
-        <v>69000</v>
+        <v>19000</v>
       </c>
       <c r="F83" s="3">
-        <v>77000</v>
+        <v>19000</v>
       </c>
       <c r="G83" s="3">
-        <v>77000</v>
+        <v>17000</v>
       </c>
       <c r="H83" s="3">
-        <v>75000</v>
+        <v>22000</v>
       </c>
       <c r="I83" s="3">
-        <v>74000</v>
+        <v>19000</v>
       </c>
       <c r="J83" s="3">
+        <v>19000</v>
+      </c>
+      <c r="K83" s="3">
         <v>79000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>73000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>76000</v>
       </c>
       <c r="M83" s="3">
         <v>76000</v>
       </c>
       <c r="N83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="O83" s="3">
         <v>48000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>52000</v>
       </c>
       <c r="P83" s="3">
         <v>52000</v>
       </c>
       <c r="Q83" s="3">
+        <v>52000</v>
+      </c>
+      <c r="R83" s="3">
         <v>50000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>67000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>52000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>74000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>70000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>69000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>27000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>26000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>25000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6168,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6248,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6328,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6408,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6488,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E89" s="3">
         <v>110000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>297000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>144000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>74000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>188000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>146000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>54000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-118000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>114000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>49000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>32000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>167000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>97000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>177000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>55000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>150000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>92000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>28000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>25000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>40000</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,8 +6600,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6395,70 +6616,73 @@
         <v>-22000</v>
       </c>
       <c r="G91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="H91" s="3">
         <v>-18000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-25000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-21000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-22000</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-12000</v>
       </c>
       <c r="N91" s="3">
         <v>-12000</v>
       </c>
       <c r="O91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="P91" s="3">
         <v>-9000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-18000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-14000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6000</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-11000</v>
       </c>
       <c r="V91" s="3">
         <v>-11000</v>
       </c>
       <c r="W91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="X91" s="3">
         <v>-13000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-22000</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6758,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,85 +6838,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-601000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-22000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-26000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-55000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-27000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>30000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2884000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-40000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-46000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-23000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-323000</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-1000</v>
       </c>
       <c r="T94" s="3">
         <v>-1000</v>
       </c>
       <c r="U94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V94" s="3">
         <v>-15000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1728000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-10000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-22000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>18600</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,31 +6950,32 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6794,8 +7028,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7108,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7188,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,235 +7268,247 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E100" s="3">
         <v>570000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-213000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-279000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-21000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-16000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-216000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-17000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-45000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1831000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>288000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>442000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>223000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-235000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>139000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1398000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>25000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G101" s="3">
+        <v>8000</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>8000</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="P101" s="3">
         <v>-4000</v>
       </c>
-      <c r="F101" s="3">
-        <v>7000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="Q101" s="3">
         <v>2000</v>
       </c>
-      <c r="I101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>8000</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="R101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="P101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3">
-        <v>4000</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>3</v>
+      <c r="Z101" s="3">
+        <v>0</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E102" s="3">
         <v>78000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-232000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>18000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>92000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-242000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>209000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>65000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1173000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>361000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>441000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>233000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>48000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>90000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-59000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>180000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-181000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>107000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>APG</t>
   </si>
@@ -656,366 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43159</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1861000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1826000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1730000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1601000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1759000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1784000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1771000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1614000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1703000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1735000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1649000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1471000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1112000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1047000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>978000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>803000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>882000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>958000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>889000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>858000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>985000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1118000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1067000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>922000</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1286000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1259000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1186000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1109000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1251000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1273000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1275000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1189000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1237000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1293000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1212000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1095000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>838000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>795000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>746000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>622000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>684000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>736000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>692000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>696000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>787000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>885000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>859000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>759000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>400</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>575000</v>
+      </c>
+      <c r="E10" s="3">
         <v>567000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>544000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>492000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>508000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>511000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>496000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>425000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>466000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>442000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>437000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>376000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>274000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>252000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>232000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>181000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>198000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>222000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>197000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>162000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>198000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>233000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>208000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>163000</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1044,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1124,8 +1137,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1204,88 +1220,94 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-12000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>19000</v>
       </c>
-      <c r="G14" s="3">
-        <v>4000</v>
-      </c>
       <c r="H14" s="3">
+        <v>23000</v>
+      </c>
+      <c r="I14" s="3">
         <v>22000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>3000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>12000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>11000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>24000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>9000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-11000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-4000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>208000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>12000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1293,40 +1315,40 @@
         <v>57000</v>
       </c>
       <c r="E15" s="3">
+        <v>57000</v>
+      </c>
+      <c r="F15" s="3">
         <v>52000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>50000</v>
       </c>
-      <c r="G15" s="3">
-        <v>-147000</v>
-      </c>
       <c r="H15" s="3">
+        <v>50000</v>
+      </c>
+      <c r="I15" s="3">
         <v>49000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>50000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>48000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>54000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>36000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>53000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>54000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>32000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>30000</v>
       </c>
       <c r="Q15" s="3">
         <v>30000</v>
@@ -1338,34 +1360,37 @@
         <v>30000</v>
       </c>
       <c r="T15" s="3">
+        <v>30000</v>
+      </c>
+      <c r="U15" s="3">
         <v>25000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>28000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>30000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>29000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>8000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>9000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>25000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>200</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1391,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1747000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1689000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1606000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1501000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1681000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1662000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1677000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1661000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1538000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1654000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1669000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1590000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1478000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1062000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1006000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>940000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>805000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>903000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>896000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>858000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1092000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1146000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1105000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1004000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>896000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>164900</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E18" s="3">
         <v>137000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>124000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>100000</v>
       </c>
-      <c r="G18" s="3">
-        <v>78000</v>
-      </c>
       <c r="H18" s="3">
+        <v>97000</v>
+      </c>
+      <c r="I18" s="3">
         <v>107000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>110000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>76000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>49000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>66000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>59000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>50000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>41000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>38000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-21000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>62000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>31000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-234000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-161000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>13000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>63000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>26000</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1581,408 +1613,424 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E20" s="3">
         <v>28000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-16000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-26000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>13000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>14000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>13000</v>
       </c>
       <c r="M20" s="3">
         <v>13000</v>
       </c>
       <c r="N20" s="3">
+        <v>13000</v>
+      </c>
+      <c r="O20" s="3">
         <v>11000</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>3000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>14000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>6000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>7000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>25000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>8000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2000</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>183000</v>
+      </c>
+      <c r="E21" s="3">
         <v>166000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>182000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>166000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-66000</v>
-      </c>
       <c r="H21" s="3">
+        <v>148000</v>
+      </c>
+      <c r="I21" s="3">
         <v>182000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>147000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>126000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>142000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>152000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>148000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>80000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>98000</v>
-      </c>
-      <c r="P21" s="3">
-        <v>96000</v>
       </c>
       <c r="Q21" s="3">
         <v>96000</v>
       </c>
       <c r="R21" s="3">
+        <v>96000</v>
+      </c>
+      <c r="S21" s="3">
         <v>51000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>60000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>120000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>112000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-161000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-67000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>48000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>90000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>53000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E22" s="3">
         <v>41000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>35000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>34000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>33000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>37000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>38000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>37000</v>
       </c>
       <c r="K22" s="3">
         <v>37000</v>
       </c>
       <c r="L22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="M22" s="3">
         <v>33000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>28000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>27000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>17000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>14000</v>
       </c>
       <c r="Q22" s="3">
         <v>14000</v>
       </c>
       <c r="R22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="S22" s="3">
         <v>15000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>13000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>14000</v>
       </c>
       <c r="V22" s="3">
         <v>14000</v>
       </c>
       <c r="W22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="X22" s="3">
         <v>15000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>7000</v>
       </c>
       <c r="Y22" s="3">
         <v>7000</v>
       </c>
       <c r="Z22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>6000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>159600</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E23" s="3">
         <v>100000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>89000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>63000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>45000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>74000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>75000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>38000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>26000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>46000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>44000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-23000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>33000</v>
-      </c>
-      <c r="P23" s="3">
-        <v>30000</v>
       </c>
       <c r="Q23" s="3">
         <v>30000</v>
       </c>
       <c r="R23" s="3">
+        <v>30000</v>
+      </c>
+      <c r="S23" s="3">
         <v>-14000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-18000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>55000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>24000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-245000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-151000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>14000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>57000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>22000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-159600</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E24" s="3">
         <v>31000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>20000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>18000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>20000</v>
       </c>
       <c r="H24" s="3">
         <v>20000</v>
       </c>
       <c r="I24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="J24" s="3">
         <v>27000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>18000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-16000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>18000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-6000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>28000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-12000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-51000</v>
-      </c>
-      <c r="W24" s="3">
-        <v>2000</v>
       </c>
       <c r="X24" s="3">
         <v>2000</v>
       </c>
       <c r="Y24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z24" s="3">
         <v>4000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-159600</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2061,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>69000</v>
+        <v>67000</v>
       </c>
       <c r="E26" s="3">
         <v>69000</v>
       </c>
       <c r="F26" s="3">
+        <v>69000</v>
+      </c>
+      <c r="G26" s="3">
         <v>45000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>25000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>54000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>48000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>26000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>22000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>28000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>30000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>15000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>19000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>21000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-22000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>27000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>36000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-194000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-153000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>12000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>53000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>21000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-159600</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E27" s="3">
         <v>62000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>69000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-327000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-236000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>35000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>28000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>12000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-169000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>19000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>21000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-244000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>27000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>36000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-194000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-153000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>12000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>53000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>21000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-159600</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2301,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2381,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2461,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2541,168 +2607,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-28000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>16000</v>
       </c>
-      <c r="G32" s="3">
-        <v>3000</v>
-      </c>
       <c r="H32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I32" s="3">
         <v>26000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-13000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-14000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-13000</v>
       </c>
       <c r="M32" s="3">
         <v>-13000</v>
       </c>
       <c r="N32" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="O32" s="3">
         <v>-11000</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-14000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-6000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-7000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-25000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>69000</v>
+        <v>67000</v>
       </c>
       <c r="E33" s="3">
         <v>69000</v>
       </c>
       <c r="F33" s="3">
+        <v>69000</v>
+      </c>
+      <c r="G33" s="3">
         <v>45000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>25000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>54000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>48000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>26000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-169000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>19000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>21000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-244000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>27000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>36000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-194000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-153000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>12000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>53000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>21000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-159600</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2781,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>69000</v>
+        <v>67000</v>
       </c>
       <c r="E35" s="3">
         <v>69000</v>
       </c>
       <c r="F35" s="3">
+        <v>69000</v>
+      </c>
+      <c r="G35" s="3">
         <v>45000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>25000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>54000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>48000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>26000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-169000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>19000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>21000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-244000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>27000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>36000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-194000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-153000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>12000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>53000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>21000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-159600</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43159</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2976,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3006,71 +3091,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>499000</v>
+      </c>
+      <c r="E41" s="3">
         <v>487000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>324000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>247000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>479000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>461000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>368000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>363000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>605000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>395000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>330000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>315000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1188000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1128000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>686000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>745000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>515000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>467000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>377000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>436000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3086,8 +3172,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3166,8 +3255,11 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3175,62 +3267,62 @@
         <v>1897000</v>
       </c>
       <c r="E43" s="3">
+        <v>1897000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1823000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1714000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1831000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1810000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1827000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1711000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1772000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1760000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1712000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1636000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>984000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>947000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>848000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>747000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>781000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>906000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>891000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>913000</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3246,71 +3338,74 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>155000</v>
+        <v>143000</v>
       </c>
       <c r="E44" s="3">
         <v>155000</v>
       </c>
       <c r="F44" s="3">
+        <v>155000</v>
+      </c>
+      <c r="G44" s="3">
         <v>148000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>150000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>155000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>170000</v>
-      </c>
-      <c r="J44" s="3">
-        <v>163000</v>
       </c>
       <c r="K44" s="3">
         <v>163000</v>
       </c>
       <c r="L44" s="3">
+        <v>163000</v>
+      </c>
+      <c r="M44" s="3">
         <v>150000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>149000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>142000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>69000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>71000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>69000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>66000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>64000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>57000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>60000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>59000</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,8 +3421,11 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3352,45 +3450,45 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>112000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>167000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>170000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>134000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>385000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>93000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>82000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>75000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>77000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>74000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>66000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>42000</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3406,71 +3504,74 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2658000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2691000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2454000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2232000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2582000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2652000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2532000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2364000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2652000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2472000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2361000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2227000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2626000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2239000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1685000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1633000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1437000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1504000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1394000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1450000</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3486,35 +3587,38 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E47" s="3">
         <v>6000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>29000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>27000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>42000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>31000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8000</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -3566,71 +3670,74 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>647000</v>
+      </c>
+      <c r="E48" s="3">
         <v>651000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>634000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>609000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>618000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>604000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>639000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>621000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>629000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>608000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>614000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>628000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>427000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>439000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>453000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>459000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>462000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>452000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>467000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>500000</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3646,71 +3753,74 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4554000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4663000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4598000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4020000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4091000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4028000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4147000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4139000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4166000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4010000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4254000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4492000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1988000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1996000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1991000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2008000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2047000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1772000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1799000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1836000</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3726,8 +3836,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3806,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3886,71 +4002,74 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E52" s="3">
         <v>166000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>196000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>189000</v>
       </c>
-      <c r="G52" s="3">
-        <v>175000</v>
-      </c>
       <c r="H52" s="3">
+        <v>128000</v>
+      </c>
+      <c r="I52" s="3">
         <v>516000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>519000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>523000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>644000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>851000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>825000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>795000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>118000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>109000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>114000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>118000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>119000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>98000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>110000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>100000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3966,8 +4085,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4046,71 +4168,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8152000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8245000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7961000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7192000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7590000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7949000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7974000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7766000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8091000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7941000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8054000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8142000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5159000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4783000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4243000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4218000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4065000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3826000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3770000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3886000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4126,8 +4251,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4156,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4186,71 +4315,72 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>497000</v>
+      </c>
+      <c r="E57" s="3">
         <v>454000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>424000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>382000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>472000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>431000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>473000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>442000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>490000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>469000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>448000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>391000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>236000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>205000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>180000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>167000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>150000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>142000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>155000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>152000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4266,8 +4396,11 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4275,62 +4408,62 @@
         <v>94000</v>
       </c>
       <c r="E58" s="3">
+        <v>94000</v>
+      </c>
+      <c r="F58" s="3">
         <v>86000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>180000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>80000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>328000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>79000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>78000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>212000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>28000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>29000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>42000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>63000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>49000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>44000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>45000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>244000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4346,71 +4479,74 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>625000</v>
+      </c>
+      <c r="E59" s="3">
         <v>608000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>590000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>587000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>548000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>515000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>523000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>518000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1219000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1043000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>998000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>971000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>603000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>558000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>508000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>551000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>642000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>648000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>621000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>523000</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4426,71 +4562,74 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1885000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1781000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1662000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1654000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1807000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1899000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1651000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1549000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1921000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1523000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1453000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1367000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>867000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>792000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>730000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>781000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>841000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>834000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>821000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>919000</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4506,71 +4645,74 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2941000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3044000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3029000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2797000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2494000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2512000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2758000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2743000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2595000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2791000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2823000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2819000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1845000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1548000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1538000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1475000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1493000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1248000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1254000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1260000</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4586,71 +4728,74 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E62" s="3">
         <v>153000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>149000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>156000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>90000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>132000</v>
       </c>
       <c r="I62" s="3">
         <v>132000</v>
       </c>
       <c r="J62" s="3">
+        <v>132000</v>
+      </c>
+      <c r="K62" s="3">
         <v>130000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>651000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>680000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>825000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>881000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>124000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>146000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>147000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>171000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>173000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>146000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>130000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>182000</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4666,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4746,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4826,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4906,71 +5060,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5199000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5278000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5126000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4891000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4722000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4920000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4930000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4804000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5167000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4994000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5101000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5067000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2836000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2486000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2415000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2427000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2507000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2228000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2205000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2361000</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4986,8 +5143,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5016,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5096,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5176,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5191,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>797000</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
         <v>797000</v>
@@ -5215,7 +5382,7 @@
         <v>797000</v>
       </c>
       <c r="O70" s="3">
-        <v>0</v>
+        <v>797000</v>
       </c>
       <c r="P70" s="3">
         <v>0</v>
@@ -5256,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5336,71 +5506,74 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E72" s="3">
         <v>148000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>79000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-36000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-90000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-138000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-164000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-186000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-214000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-255000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-237000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-252000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-271000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-292000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-284000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-262000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-289000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-325000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5410,14 +5583,17 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA72" s="3">
-        <v>0</v>
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5496,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5576,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5656,71 +5838,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2953000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2967000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2835000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2301000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2071000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2232000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2247000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2165000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2127000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2150000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2156000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2278000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2323000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2297000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1828000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1791000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1558000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1598000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1565000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1525000</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5736,8 +5921,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5816,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43159</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>69000</v>
+        <v>67000</v>
       </c>
       <c r="E81" s="3">
         <v>69000</v>
       </c>
       <c r="F81" s="3">
+        <v>69000</v>
+      </c>
+      <c r="G81" s="3">
         <v>45000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>25000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>54000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>48000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>26000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-169000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>19000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>21000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-244000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>27000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>36000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-194000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-153000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>12000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>53000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>21000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-159600</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6011,88 +6208,92 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E83" s="3">
         <v>21000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>19000</v>
       </c>
       <c r="F83" s="3">
         <v>19000</v>
       </c>
       <c r="G83" s="3">
+        <v>19000</v>
+      </c>
+      <c r="H83" s="3">
         <v>17000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>22000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>19000</v>
       </c>
       <c r="J83" s="3">
         <v>19000</v>
       </c>
       <c r="K83" s="3">
+        <v>19000</v>
+      </c>
+      <c r="L83" s="3">
         <v>79000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>73000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>76000</v>
       </c>
       <c r="N83" s="3">
         <v>76000</v>
       </c>
       <c r="O83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="P83" s="3">
         <v>48000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>52000</v>
       </c>
       <c r="Q83" s="3">
         <v>52000</v>
       </c>
       <c r="R83" s="3">
+        <v>52000</v>
+      </c>
+      <c r="S83" s="3">
         <v>50000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>67000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>52000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>74000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>70000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>69000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>27000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>26000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>25000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6171,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6251,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6331,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6411,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6491,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>283000</v>
+      </c>
+      <c r="E89" s="3">
         <v>220000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>110000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>297000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>144000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>74000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>188000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>146000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>54000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-118000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>114000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>49000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-13000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>32000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>167000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>97000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>177000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>55000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>150000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>92000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>28000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>25000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>40000</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6601,13 +6820,14 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-22000</v>
+        <v>-18000</v>
       </c>
       <c r="E91" s="3">
         <v>-22000</v>
@@ -6619,70 +6839,73 @@
         <v>-22000</v>
       </c>
       <c r="H91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-18000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-25000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-22000</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-12000</v>
       </c>
       <c r="O91" s="3">
         <v>-12000</v>
       </c>
       <c r="P91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-18000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-14000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6000</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-11000</v>
       </c>
       <c r="W91" s="3">
         <v>-11000</v>
       </c>
       <c r="X91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-18000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6761,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6841,88 +7067,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-149000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-57000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-601000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-22000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-26000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-55000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>30000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-28000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2884000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-40000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-46000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-23000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-323000</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-1000</v>
       </c>
       <c r="U94" s="3">
         <v>-1000</v>
       </c>
       <c r="V94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="W94" s="3">
         <v>-15000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1728000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-22000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>18600</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6951,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6977,8 +7210,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7031,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7111,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7191,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7271,244 +7513,256 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-103000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>570000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-213000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-279000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-21000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-16000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-216000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-17000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-45000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1831000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>288000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>442000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-36000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>223000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>200000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-5000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-235000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>139000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1398000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>25000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5000</v>
-      </c>
-      <c r="E101" s="3">
-        <v>2000</v>
       </c>
       <c r="F101" s="3">
         <v>2000</v>
       </c>
       <c r="G101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H101" s="3">
         <v>8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-7000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>8000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-7000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1000</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>3</v>
+      <c r="AA101" s="3">
+        <v>0</v>
       </c>
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E102" s="3">
         <v>163000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>78000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-232000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>18000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>92000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-242000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>209000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>65000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1173000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>361000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>441000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-59000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>233000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>48000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>90000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-59000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>180000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-181000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>107000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-13000</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
   <si>
     <t>APG</t>
   </si>
@@ -656,378 +656,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43159</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1719000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1861000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1826000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1730000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1601000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1759000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1784000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1771000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1614000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1703000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1735000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1649000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1471000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1112000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1047000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>978000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>803000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>882000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>958000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>889000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>858000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>985000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1118000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1067000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>922000</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1177000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1286000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1259000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1186000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1109000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1251000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1273000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1275000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1189000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1237000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1293000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1212000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1095000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>838000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>795000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>746000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>622000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>684000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>736000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>692000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>696000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>787000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>885000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>859000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>759000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>400</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>542000</v>
+      </c>
+      <c r="E10" s="3">
         <v>575000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>567000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>544000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>492000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>508000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>511000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>496000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>425000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>466000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>442000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>437000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>376000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>274000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>252000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>232000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>181000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>198000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>222000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>197000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>162000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>198000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>233000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>208000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>163000</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,8 +1070,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,91 +1240,97 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E14" s="3">
         <v>7000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>-12000</v>
       </c>
-      <c r="G14" s="3">
-        <v>19000</v>
-      </c>
       <c r="H14" s="3">
+        <v>12000</v>
+      </c>
+      <c r="I14" s="3">
         <v>23000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>22000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>3000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>12000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>11000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>24000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>9000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-11000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-4000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>208000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>12000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1318,40 +1341,40 @@
         <v>57000</v>
       </c>
       <c r="F15" s="3">
+        <v>57000</v>
+      </c>
+      <c r="G15" s="3">
         <v>52000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>50000</v>
       </c>
       <c r="H15" s="3">
         <v>50000</v>
       </c>
       <c r="I15" s="3">
+        <v>50000</v>
+      </c>
+      <c r="J15" s="3">
         <v>49000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>50000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>48000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>54000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>36000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>53000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>54000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>32000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>30000</v>
       </c>
       <c r="R15" s="3">
         <v>30000</v>
@@ -1363,34 +1386,37 @@
         <v>30000</v>
       </c>
       <c r="U15" s="3">
+        <v>30000</v>
+      </c>
+      <c r="V15" s="3">
         <v>25000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>28000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>30000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>29000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>8000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>9000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>25000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>200</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1613000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1747000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1689000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1606000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1501000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1493000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1662000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1677000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1661000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1538000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1654000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1669000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1590000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1478000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1062000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1006000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>940000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>805000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>903000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>896000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>858000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1092000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1146000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1105000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1004000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>896000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>164900</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E18" s="3">
         <v>114000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>137000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>124000</v>
       </c>
-      <c r="G18" s="3">
-        <v>100000</v>
-      </c>
       <c r="H18" s="3">
+        <v>108000</v>
+      </c>
+      <c r="I18" s="3">
         <v>97000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>107000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>110000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>76000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>49000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>66000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>59000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>50000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>41000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>38000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-21000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>62000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>31000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-234000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-161000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>13000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>63000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>26000</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,340 +1647,353 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>-12000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>28000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-16000</v>
       </c>
       <c r="H20" s="3">
         <v>-1000</v>
       </c>
       <c r="I20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-26000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>13000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>14000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>13000</v>
       </c>
       <c r="N20" s="3">
         <v>13000</v>
       </c>
       <c r="O20" s="3">
+        <v>13000</v>
+      </c>
+      <c r="P20" s="3">
         <v>11000</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>3000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>14000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>6000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>7000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>25000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>8000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2000</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E21" s="3">
         <v>183000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>166000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>182000</v>
       </c>
-      <c r="G21" s="3">
-        <v>166000</v>
-      </c>
       <c r="H21" s="3">
+        <v>159000</v>
+      </c>
+      <c r="I21" s="3">
         <v>148000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>182000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>147000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>126000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>142000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>152000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>148000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>80000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>98000</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>96000</v>
       </c>
       <c r="R21" s="3">
         <v>96000</v>
       </c>
       <c r="S21" s="3">
+        <v>96000</v>
+      </c>
+      <c r="T21" s="3">
         <v>51000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>60000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>120000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>112000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-161000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-67000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>48000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>90000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>53000</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E22" s="3">
         <v>36000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>41000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>35000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>34000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>33000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>37000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>38000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>37000</v>
       </c>
       <c r="L22" s="3">
         <v>37000</v>
       </c>
       <c r="M22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="N22" s="3">
         <v>33000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>28000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>27000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>17000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>14000</v>
       </c>
       <c r="R22" s="3">
         <v>14000</v>
       </c>
       <c r="S22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="T22" s="3">
         <v>15000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>11000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>13000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>14000</v>
       </c>
       <c r="W22" s="3">
         <v>14000</v>
       </c>
       <c r="X22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>15000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>7000</v>
       </c>
       <c r="Z22" s="3">
         <v>7000</v>
       </c>
       <c r="AA22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AB22" s="3">
         <v>6000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>159600</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E23" s="3">
         <v>78000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>100000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>89000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>63000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>45000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>74000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>75000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>38000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>26000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>46000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>44000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-23000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>33000</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>30000</v>
       </c>
       <c r="R23" s="3">
         <v>30000</v>
       </c>
       <c r="S23" s="3">
+        <v>30000</v>
+      </c>
+      <c r="T23" s="3">
         <v>-14000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-18000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>55000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>24000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-245000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-151000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>14000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>57000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>22000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-159600</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1955,82 +2001,85 @@
         <v>11000</v>
       </c>
       <c r="E24" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F24" s="3">
         <v>31000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>20000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>18000</v>
-      </c>
-      <c r="H24" s="3">
-        <v>20000</v>
       </c>
       <c r="I24" s="3">
         <v>20000</v>
       </c>
       <c r="J24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="K24" s="3">
         <v>27000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>18000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-16000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>18000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>11000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-6000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>28000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-12000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-51000</v>
-      </c>
-      <c r="X24" s="3">
-        <v>2000</v>
       </c>
       <c r="Y24" s="3">
         <v>2000</v>
       </c>
       <c r="Z24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA24" s="3">
         <v>4000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-159600</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E26" s="3">
         <v>67000</v>
-      </c>
-      <c r="E26" s="3">
-        <v>69000</v>
       </c>
       <c r="F26" s="3">
         <v>69000</v>
       </c>
       <c r="G26" s="3">
+        <v>69000</v>
+      </c>
+      <c r="H26" s="3">
         <v>45000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>25000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>54000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>48000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>26000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>22000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>28000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>30000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>15000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>21000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-22000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>27000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>36000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-194000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-153000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>12000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>53000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>21000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-159600</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-28000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>62000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>69000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-327000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-334000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-236000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>35000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>28000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>12000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>11000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-169000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>21000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-244000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>27000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>36000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-194000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-153000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>12000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>53000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>21000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-159600</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,174 +2677,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>12000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-28000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>16000</v>
       </c>
       <c r="H32" s="3">
         <v>1000</v>
       </c>
       <c r="I32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J32" s="3">
         <v>26000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-13000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-14000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-13000</v>
       </c>
       <c r="N32" s="3">
         <v>-13000</v>
       </c>
       <c r="O32" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="P32" s="3">
         <v>-11000</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-3000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-14000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-6000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-7000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-25000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E33" s="3">
         <v>67000</v>
-      </c>
-      <c r="E33" s="3">
-        <v>69000</v>
       </c>
       <c r="F33" s="3">
         <v>69000</v>
       </c>
       <c r="G33" s="3">
+        <v>69000</v>
+      </c>
+      <c r="H33" s="3">
         <v>45000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>25000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>54000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>48000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>26000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>11000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-169000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>21000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-244000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>27000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>36000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-194000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-153000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>12000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>53000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>21000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-159600</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E35" s="3">
         <v>67000</v>
-      </c>
-      <c r="E35" s="3">
-        <v>69000</v>
       </c>
       <c r="F35" s="3">
         <v>69000</v>
       </c>
       <c r="G35" s="3">
+        <v>69000</v>
+      </c>
+      <c r="H35" s="3">
         <v>45000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>25000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>54000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>48000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>26000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>11000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-169000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>21000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-244000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>27000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>36000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-194000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-153000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>12000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>53000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>21000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-159600</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43159</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,74 +3178,75 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>460000</v>
+      </c>
+      <c r="E41" s="3">
         <v>499000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>487000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>324000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>247000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>479000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>461000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>368000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>363000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>605000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>395000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>330000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>315000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1188000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1128000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>686000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>745000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>515000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>467000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>377000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>436000</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,8 +3262,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,74 +3348,77 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1897000</v>
+        <v>1841000</v>
       </c>
       <c r="E43" s="3">
         <v>1897000</v>
       </c>
       <c r="F43" s="3">
+        <v>1897000</v>
+      </c>
+      <c r="G43" s="3">
         <v>1823000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1714000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1831000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1810000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1827000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1711000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1772000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1760000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1712000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1636000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>984000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>947000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>848000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>747000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>781000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>906000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>891000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>913000</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,74 +3434,77 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E44" s="3">
         <v>143000</v>
-      </c>
-      <c r="E44" s="3">
-        <v>155000</v>
       </c>
       <c r="F44" s="3">
         <v>155000</v>
       </c>
       <c r="G44" s="3">
+        <v>155000</v>
+      </c>
+      <c r="H44" s="3">
         <v>148000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>150000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>155000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>170000</v>
-      </c>
-      <c r="K44" s="3">
-        <v>163000</v>
       </c>
       <c r="L44" s="3">
         <v>163000</v>
       </c>
       <c r="M44" s="3">
+        <v>163000</v>
+      </c>
+      <c r="N44" s="3">
         <v>150000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>149000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>142000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>69000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>71000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>69000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>66000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>64000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>57000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>60000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>59000</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3424,8 +3520,11 @@
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3453,45 +3552,45 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>112000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>167000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>170000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>134000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>385000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>93000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>82000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>75000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>77000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>74000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>66000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>42000</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3507,74 +3606,77 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2586000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2658000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2691000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2454000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2232000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2582000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2652000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2532000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2364000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2652000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2472000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2361000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2227000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2626000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2239000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1685000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1633000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1437000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1504000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1394000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1450000</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3590,38 +3692,41 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E47" s="3">
         <v>29000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>29000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>27000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>42000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>31000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8000</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -3673,74 +3778,77 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>642000</v>
+      </c>
+      <c r="E48" s="3">
         <v>647000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>651000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>634000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>609000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>618000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>604000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>639000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>621000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>629000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>608000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>614000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>628000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>427000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>439000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>453000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>459000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>462000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>452000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>467000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>500000</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3756,74 +3864,77 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4575000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4554000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4663000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4598000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4020000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4091000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4028000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4147000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4139000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4166000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4010000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4254000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4492000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1988000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1996000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1991000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2008000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2047000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1772000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1799000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1836000</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,74 +4122,77 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>219000</v>
+      </c>
+      <c r="E52" s="3">
         <v>111000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>166000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>196000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>189000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>128000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>516000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>519000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>523000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>644000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>851000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>825000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>795000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>118000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>109000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>114000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>118000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>119000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>98000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>110000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>100000</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,74 +4294,77 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8098000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8152000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8245000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7961000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7192000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7590000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7949000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7974000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7766000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8091000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7941000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8054000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8142000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5159000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4783000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4243000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4218000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4065000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3826000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3770000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3886000</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4254,8 +4380,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,74 +4446,75 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>450000</v>
+      </c>
+      <c r="E57" s="3">
         <v>497000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>454000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>424000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>382000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>472000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>431000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>473000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>442000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>490000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>469000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>448000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>391000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>236000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>205000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>180000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>167000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>150000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>142000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>155000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>152000</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4399,74 +4530,77 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>94000</v>
+        <v>95000</v>
       </c>
       <c r="E58" s="3">
         <v>94000</v>
       </c>
       <c r="F58" s="3">
+        <v>94000</v>
+      </c>
+      <c r="G58" s="3">
         <v>86000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>180000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>80000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>328000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>79000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>78000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>212000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>28000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>29000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>42000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>63000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>49000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>44000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>45000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>244000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4482,74 +4616,77 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>661000</v>
+      </c>
+      <c r="E59" s="3">
         <v>625000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>608000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>590000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>587000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>548000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>515000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>523000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>518000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1219000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1043000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>998000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>971000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>603000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>558000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>508000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>551000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>642000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>648000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>621000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>523000</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4565,74 +4702,77 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1762000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1885000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1781000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1662000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1654000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1807000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1899000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1651000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1549000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1921000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1523000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1453000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1367000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>867000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>792000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>730000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>781000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>841000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>834000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>821000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>919000</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4648,74 +4788,77 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2942000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2941000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3044000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3029000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2797000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2494000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2512000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2758000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2743000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2595000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2791000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2823000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2819000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1845000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1548000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1538000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1475000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1493000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1248000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1254000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1260000</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4731,74 +4874,77 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E62" s="3">
         <v>85000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>153000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>149000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>156000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>90000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>132000</v>
       </c>
       <c r="J62" s="3">
         <v>132000</v>
       </c>
       <c r="K62" s="3">
+        <v>132000</v>
+      </c>
+      <c r="L62" s="3">
         <v>130000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>651000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>680000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>825000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>881000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>124000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>146000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>147000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>171000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>173000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>146000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>130000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>182000</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,74 +5218,77 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5116000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5199000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5278000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5126000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4891000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4722000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4920000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4930000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4804000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5167000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4994000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5101000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5067000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2836000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2486000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2415000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2427000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2507000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2228000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2205000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2361000</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5146,8 +5304,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5361,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>797000</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
         <v>797000</v>
@@ -5385,7 +5553,7 @@
         <v>797000</v>
       </c>
       <c r="P70" s="3">
-        <v>0</v>
+        <v>797000</v>
       </c>
       <c r="Q70" s="3">
         <v>0</v>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,74 +5680,77 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>250000</v>
+      </c>
+      <c r="E72" s="3">
         <v>215000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>148000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>79000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-11000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-36000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-90000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-138000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-164000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-186000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-214000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-255000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-237000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-252000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-271000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-292000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-284000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-262000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-289000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-325000</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5586,14 +5760,17 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB72" s="3">
-        <v>0</v>
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,74 +6024,77 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2982000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2953000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2967000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2835000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2301000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2071000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2232000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2247000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2165000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2127000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2150000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2156000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2278000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2323000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2297000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1828000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1791000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1558000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1598000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1565000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1525000</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5924,8 +6110,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43159</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E81" s="3">
         <v>67000</v>
-      </c>
-      <c r="E81" s="3">
-        <v>69000</v>
       </c>
       <c r="F81" s="3">
         <v>69000</v>
       </c>
       <c r="G81" s="3">
+        <v>69000</v>
+      </c>
+      <c r="H81" s="3">
         <v>45000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>25000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>54000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>48000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>26000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>11000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-169000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>21000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-244000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>27000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>36000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-194000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-153000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>12000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>53000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>21000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-159600</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,91 +6407,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E83" s="3">
         <v>20000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>19000</v>
       </c>
       <c r="G83" s="3">
         <v>19000</v>
       </c>
       <c r="H83" s="3">
+        <v>19000</v>
+      </c>
+      <c r="I83" s="3">
         <v>17000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>22000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>19000</v>
       </c>
       <c r="K83" s="3">
         <v>19000</v>
       </c>
       <c r="L83" s="3">
+        <v>19000</v>
+      </c>
+      <c r="M83" s="3">
         <v>79000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>73000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>76000</v>
       </c>
       <c r="O83" s="3">
         <v>76000</v>
       </c>
       <c r="P83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>48000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>52000</v>
       </c>
       <c r="R83" s="3">
         <v>52000</v>
       </c>
       <c r="S83" s="3">
+        <v>52000</v>
+      </c>
+      <c r="T83" s="3">
         <v>50000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>67000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>52000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>74000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>70000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>69000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>27000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>26000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>25000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E89" s="3">
         <v>283000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>220000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>110000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>297000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>144000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>74000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>188000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>146000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>54000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-118000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>114000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>49000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-13000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>32000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>167000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>97000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>177000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>55000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>150000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>92000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>28000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>25000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>40000</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,16 +7041,17 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18000</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-22000</v>
       </c>
       <c r="F91" s="3">
         <v>-22000</v>
@@ -6842,70 +7063,73 @@
         <v>-22000</v>
       </c>
       <c r="I91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="J91" s="3">
         <v>-18000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-25000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-21000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-22000</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-12000</v>
       </c>
       <c r="P91" s="3">
         <v>-12000</v>
       </c>
       <c r="Q91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="R91" s="3">
         <v>-9000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-18000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-14000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6000</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-11000</v>
       </c>
       <c r="X91" s="3">
         <v>-11000</v>
       </c>
       <c r="Y91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7297,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-149000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-57000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-601000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-22000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-26000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-55000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>30000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-28000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2884000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-40000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-46000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-23000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-323000</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-1000</v>
       </c>
       <c r="V94" s="3">
         <v>-1000</v>
       </c>
       <c r="W94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="X94" s="3">
         <v>-15000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1728000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-22000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>18600</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7213,8 +7447,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,253 +7759,265 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-98000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-103000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>570000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-213000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-279000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-21000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-16000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-216000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-45000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-13000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1831000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>288000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>442000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-36000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>223000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>200000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-235000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>139000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1398000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>25000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E101" s="3">
         <v>7000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>2000</v>
       </c>
       <c r="G101" s="3">
         <v>2000</v>
       </c>
       <c r="H101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I101" s="3">
         <v>8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-7000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>8000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-8000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-7000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>3</v>
+      <c r="AB101" s="3">
+        <v>0</v>
       </c>
       <c r="AC101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E102" s="3">
         <v>12000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>163000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>78000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-232000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>18000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>92000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-242000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>209000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>65000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1173000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>361000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>441000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-59000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>233000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>48000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>90000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-59000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>180000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-181000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>107000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
   <si>
     <t>APG</t>
   </si>
@@ -656,391 +656,404 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43159</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1990000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1719000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1861000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1826000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1730000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1601000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1759000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1784000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1771000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1614000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1703000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1735000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1649000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1471000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1112000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1047000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>978000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>803000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>882000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>958000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>889000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>858000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>985000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1118000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1067000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>922000</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1375000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1177000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1286000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1259000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1186000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1109000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1251000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1273000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1275000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1189000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1237000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1293000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1212000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1095000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>838000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>795000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>746000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>622000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>684000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>736000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>692000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>696000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>787000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>885000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>859000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>759000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>400</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>615000</v>
+      </c>
+      <c r="E10" s="3">
         <v>542000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>575000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>567000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>544000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>492000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>508000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>511000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>496000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>425000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>466000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>442000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>437000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>376000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>274000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>252000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>232000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>181000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>198000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>222000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>197000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>162000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>198000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>233000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>208000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>163000</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,8 +1084,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1157,8 +1171,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,99 +1260,105 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>7000</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J14" s="3">
+        <v>23000</v>
+      </c>
+      <c r="K14" s="3">
         <v>22000</v>
       </c>
-      <c r="E14" s="3">
-        <v>7000</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N14" s="3">
         <v>12000</v>
       </c>
-      <c r="I14" s="3">
-        <v>23000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>22000</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>3000</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P14" s="3">
+        <v>11000</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>24000</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>9000</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="X14" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>208000</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>12000</v>
       </c>
-      <c r="N14" s="3">
-        <v>2000</v>
-      </c>
-      <c r="O14" s="3">
-        <v>11000</v>
-      </c>
-      <c r="P14" s="3">
-        <v>24000</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
-        <v>9000</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="W14" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="X14" s="3">
-        <v>208000</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>12000</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>3</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>57000</v>
+        <v>55000</v>
       </c>
       <c r="E15" s="3">
         <v>57000</v>
@@ -1344,40 +1367,40 @@
         <v>57000</v>
       </c>
       <c r="G15" s="3">
+        <v>57000</v>
+      </c>
+      <c r="H15" s="3">
         <v>52000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>50000</v>
       </c>
       <c r="I15" s="3">
         <v>50000</v>
       </c>
       <c r="J15" s="3">
+        <v>50000</v>
+      </c>
+      <c r="K15" s="3">
         <v>49000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>50000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>48000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>54000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>36000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>53000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>54000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>32000</v>
-      </c>
-      <c r="R15" s="3">
-        <v>30000</v>
       </c>
       <c r="S15" s="3">
         <v>30000</v>
@@ -1389,34 +1412,37 @@
         <v>30000</v>
       </c>
       <c r="V15" s="3">
+        <v>30000</v>
+      </c>
+      <c r="W15" s="3">
         <v>25000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>28000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>30000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>29000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>8000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>9000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>25000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>200</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1470,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1613000</v>
+        <v>1823000</v>
       </c>
       <c r="E17" s="3">
+        <v>1620000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1747000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1689000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1606000</v>
-      </c>
       <c r="H17" s="3">
-        <v>1493000</v>
+        <v>1600000</v>
       </c>
       <c r="I17" s="3">
+        <v>1505000</v>
+      </c>
+      <c r="J17" s="3">
         <v>1662000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1677000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1661000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1538000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1654000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1669000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1590000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1478000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1062000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1006000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>940000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>805000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>903000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>896000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>858000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1092000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1146000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1105000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1004000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>896000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>164900</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>106000</v>
+        <v>167000</v>
       </c>
       <c r="E18" s="3">
+        <v>99000</v>
+      </c>
+      <c r="F18" s="3">
         <v>114000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>137000</v>
       </c>
-      <c r="G18" s="3">
-        <v>124000</v>
-      </c>
       <c r="H18" s="3">
-        <v>108000</v>
+        <v>130000</v>
       </c>
       <c r="I18" s="3">
+        <v>96000</v>
+      </c>
+      <c r="J18" s="3">
         <v>97000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>107000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>110000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>76000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>49000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>66000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>59000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>50000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>41000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>38000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-21000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>62000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>31000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-234000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-161000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>13000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>63000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>26000</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,438 +1681,454 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>-12000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>28000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-6000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-26000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>13000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>13000</v>
       </c>
       <c r="O20" s="3">
         <v>13000</v>
       </c>
       <c r="P20" s="3">
+        <v>13000</v>
+      </c>
+      <c r="Q20" s="3">
         <v>11000</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>3000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>14000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>6000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>7000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>25000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>8000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2000</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>163000</v>
+        <v>229000</v>
       </c>
       <c r="E21" s="3">
+        <v>156000</v>
+      </c>
+      <c r="F21" s="3">
         <v>183000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>166000</v>
       </c>
-      <c r="G21" s="3">
-        <v>182000</v>
-      </c>
       <c r="H21" s="3">
-        <v>159000</v>
+        <v>184000</v>
       </c>
       <c r="I21" s="3">
         <v>148000</v>
       </c>
       <c r="J21" s="3">
+        <v>148000</v>
+      </c>
+      <c r="K21" s="3">
         <v>182000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>147000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>126000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>142000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>152000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>148000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>80000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>98000</v>
-      </c>
-      <c r="R21" s="3">
-        <v>96000</v>
       </c>
       <c r="S21" s="3">
         <v>96000</v>
       </c>
       <c r="T21" s="3">
+        <v>96000</v>
+      </c>
+      <c r="U21" s="3">
         <v>51000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>60000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>120000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>112000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-161000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-67000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>48000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>90000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>53000</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E22" s="3">
         <v>38000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>36000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>41000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>35000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>34000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>33000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>37000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>38000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>37000</v>
       </c>
       <c r="M22" s="3">
         <v>37000</v>
       </c>
       <c r="N22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="O22" s="3">
         <v>33000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>28000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>27000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>17000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>14000</v>
       </c>
       <c r="S22" s="3">
         <v>14000</v>
       </c>
       <c r="T22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="U22" s="3">
         <v>15000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>11000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>13000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>14000</v>
       </c>
       <c r="X22" s="3">
         <v>14000</v>
       </c>
       <c r="Y22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>15000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>7000</v>
       </c>
       <c r="AA22" s="3">
         <v>7000</v>
       </c>
       <c r="AB22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>6000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>159600</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E23" s="3">
         <v>46000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>78000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>100000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>89000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>63000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>45000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>74000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>75000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>38000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>26000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>46000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>44000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>33000</v>
-      </c>
-      <c r="R23" s="3">
-        <v>30000</v>
       </c>
       <c r="S23" s="3">
         <v>30000</v>
       </c>
       <c r="T23" s="3">
+        <v>30000</v>
+      </c>
+      <c r="U23" s="3">
         <v>-14000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-18000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>55000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>24000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-245000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-151000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>14000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>57000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>22000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-159600</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>11000</v>
+        <v>31000</v>
       </c>
       <c r="E24" s="3">
         <v>11000</v>
       </c>
       <c r="F24" s="3">
+        <v>11000</v>
+      </c>
+      <c r="G24" s="3">
         <v>31000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>20000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>18000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>20000</v>
       </c>
       <c r="J24" s="3">
         <v>20000</v>
       </c>
       <c r="K24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L24" s="3">
         <v>27000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>18000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>18000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-6000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>28000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-12000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-51000</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>2000</v>
       </c>
       <c r="Z24" s="3">
         <v>2000</v>
       </c>
       <c r="AA24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AB24" s="3">
         <v>4000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-159600</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2213,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E26" s="3">
         <v>35000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>67000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>69000</v>
       </c>
       <c r="G26" s="3">
         <v>69000</v>
       </c>
       <c r="H26" s="3">
+        <v>69000</v>
+      </c>
+      <c r="I26" s="3">
         <v>45000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>25000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>54000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>48000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>26000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>22000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>28000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>30000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>15000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>21000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-22000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>27000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>36000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-194000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-153000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>12000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>53000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>21000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-159600</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E27" s="3">
         <v>31000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-28000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>62000</v>
       </c>
-      <c r="G27" s="3">
-        <v>69000</v>
-      </c>
       <c r="H27" s="3">
-        <v>-334000</v>
+        <v>62000</v>
       </c>
       <c r="I27" s="3">
+        <v>-327000</v>
+      </c>
+      <c r="J27" s="3">
         <v>-236000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>35000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>28000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>17000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-169000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>21000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-244000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>27000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>36000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-194000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-153000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>12000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>53000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>21000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-159600</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2480,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2569,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2658,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,180 +2747,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>12000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-28000</v>
       </c>
-      <c r="G32" s="3">
-        <v>6000</v>
-      </c>
       <c r="H32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>26000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-13000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-13000</v>
       </c>
       <c r="O32" s="3">
         <v>-13000</v>
       </c>
       <c r="P32" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-3000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-14000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-6000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-7000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-25000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E33" s="3">
         <v>35000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>67000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>69000</v>
       </c>
       <c r="G33" s="3">
         <v>69000</v>
       </c>
       <c r="H33" s="3">
+        <v>69000</v>
+      </c>
+      <c r="I33" s="3">
         <v>45000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>25000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>54000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>48000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>26000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>17000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-169000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>21000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-244000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>27000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>36000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-194000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-153000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>12000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>53000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>21000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-159600</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3014,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E35" s="3">
         <v>35000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>67000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>69000</v>
       </c>
       <c r="G35" s="3">
         <v>69000</v>
       </c>
       <c r="H35" s="3">
+        <v>69000</v>
+      </c>
+      <c r="I35" s="3">
         <v>45000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>25000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>54000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>48000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>26000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>17000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-169000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>21000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-244000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>27000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>36000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-194000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-153000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>12000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>53000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>21000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-159600</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43159</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3232,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,77 +3265,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>432000</v>
+      </c>
+      <c r="E41" s="3">
         <v>460000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>499000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>487000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>324000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>247000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>479000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>461000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>368000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>363000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>605000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>395000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>330000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>315000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1188000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1128000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>686000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>745000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>515000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>467000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>377000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>436000</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3265,8 +3352,11 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3351,77 +3441,80 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2052000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1841000</v>
-      </c>
-      <c r="E43" s="3">
-        <v>1897000</v>
       </c>
       <c r="F43" s="3">
         <v>1897000</v>
       </c>
       <c r="G43" s="3">
+        <v>1897000</v>
+      </c>
+      <c r="H43" s="3">
         <v>1823000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1714000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1831000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1810000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1827000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1711000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1772000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1760000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1712000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1636000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>984000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>947000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>848000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>747000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>781000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>906000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>891000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>913000</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3437,77 +3530,80 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E44" s="3">
         <v>150000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>143000</v>
-      </c>
-      <c r="F44" s="3">
-        <v>155000</v>
       </c>
       <c r="G44" s="3">
         <v>155000</v>
       </c>
       <c r="H44" s="3">
+        <v>155000</v>
+      </c>
+      <c r="I44" s="3">
         <v>148000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>150000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>155000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>170000</v>
-      </c>
-      <c r="L44" s="3">
-        <v>163000</v>
       </c>
       <c r="M44" s="3">
         <v>163000</v>
       </c>
       <c r="N44" s="3">
+        <v>163000</v>
+      </c>
+      <c r="O44" s="3">
         <v>150000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>149000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>142000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>69000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>71000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>69000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>66000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>64000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>57000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>60000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>59000</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3523,8 +3619,11 @@
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3555,45 +3654,45 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>112000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>167000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>170000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>134000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>385000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>93000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>82000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>75000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>77000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>74000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>66000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>42000</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,77 +3708,80 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2798000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2586000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2658000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2691000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2454000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2232000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2582000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2652000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2532000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2364000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2652000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2472000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2361000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2227000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2626000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2239000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1685000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1633000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1437000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1504000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1394000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1450000</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3695,41 +3797,44 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E47" s="3">
         <v>12000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3">
+        <v>6000</v>
+      </c>
+      <c r="H47" s="3">
         <v>29000</v>
       </c>
-      <c r="F47" s="3">
-        <v>6000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>29000</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>27000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>42000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>31000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8000</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -3781,77 +3886,80 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>672000</v>
+      </c>
+      <c r="E48" s="3">
         <v>642000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>647000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>651000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>634000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>609000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>618000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>604000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>639000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>621000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>629000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>608000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>614000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>628000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>427000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>439000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>453000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>459000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>462000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>452000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>467000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>500000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,77 +3975,80 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4798000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4575000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4554000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4663000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4598000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4020000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4091000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4028000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4147000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4139000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4166000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4010000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4254000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4492000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1988000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1996000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1991000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2008000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2047000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1772000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1799000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1836000</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3953,8 +4064,11 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4153,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,77 +4242,80 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>193000</v>
+      </c>
+      <c r="E52" s="3">
         <v>219000</v>
       </c>
-      <c r="E52" s="3">
-        <v>111000</v>
-      </c>
       <c r="F52" s="3">
+        <v>236000</v>
+      </c>
+      <c r="G52" s="3">
         <v>166000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>196000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>189000</v>
       </c>
-      <c r="I52" s="3">
-        <v>128000</v>
-      </c>
       <c r="J52" s="3">
+        <v>175000</v>
+      </c>
+      <c r="K52" s="3">
         <v>516000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>519000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>523000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>644000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>851000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>825000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>795000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>118000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>109000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>114000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>118000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>119000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>98000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>110000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>100000</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4211,8 +4331,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,77 +4420,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8539000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8098000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8152000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8245000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7961000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7192000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7590000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7949000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7974000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7766000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8091000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7941000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8054000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8142000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5159000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4783000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4243000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4218000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4065000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3826000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3770000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3886000</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4383,8 +4509,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4544,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,77 +4577,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>524000</v>
+      </c>
+      <c r="E57" s="3">
         <v>450000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>497000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>454000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>424000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>382000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>472000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>431000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>473000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>442000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>490000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>469000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>448000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>391000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>236000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>205000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>180000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>167000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>150000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>142000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>155000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>152000</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4533,77 +4664,80 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E58" s="3">
         <v>95000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>94000</v>
       </c>
       <c r="F58" s="3">
         <v>94000</v>
       </c>
       <c r="G58" s="3">
+        <v>94000</v>
+      </c>
+      <c r="H58" s="3">
         <v>86000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>180000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>80000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>328000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>79000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>78000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>212000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>28000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>29000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>42000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>63000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>49000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>44000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>45000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>244000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4619,77 +4753,80 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>685000</v>
+      </c>
+      <c r="E59" s="3">
         <v>661000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>625000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>608000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>590000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>587000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>548000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>515000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>523000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>518000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1219000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1043000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>998000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>971000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>603000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>558000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>508000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>551000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>642000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>648000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>621000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>523000</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,77 +4842,80 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1933000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1762000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1885000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1781000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1662000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1654000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1807000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1899000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1651000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1549000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1921000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1523000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1453000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1367000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>867000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>792000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>730000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>781000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>841000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>834000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>821000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>919000</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,77 +4931,80 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2959000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2942000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2941000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3044000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3029000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2797000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2494000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2512000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2758000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2743000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2595000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2791000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2823000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2819000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1845000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1548000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1538000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1475000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1493000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1248000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1254000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1260000</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4877,77 +5020,80 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>205000</v>
+      </c>
+      <c r="E62" s="3">
         <v>155000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>85000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>153000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>149000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>156000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>90000</v>
-      </c>
-      <c r="J62" s="3">
-        <v>132000</v>
       </c>
       <c r="K62" s="3">
         <v>132000</v>
       </c>
       <c r="L62" s="3">
+        <v>132000</v>
+      </c>
+      <c r="M62" s="3">
         <v>130000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>651000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>680000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>825000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>881000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>124000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>146000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>147000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>171000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>173000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>146000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>130000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>182000</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4963,8 +5109,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5198,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5287,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,77 +5376,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5368000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5116000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5199000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5278000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5126000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4891000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4722000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4920000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4930000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4804000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5167000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4994000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5101000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5067000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2836000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2486000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2415000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2427000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2507000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2228000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2205000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2361000</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5307,8 +5465,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5500,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5587,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5676,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5532,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>797000</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
         <v>797000</v>
@@ -5556,7 +5724,7 @@
         <v>797000</v>
       </c>
       <c r="Q70" s="3">
-        <v>0</v>
+        <v>797000</v>
       </c>
       <c r="R70" s="3">
         <v>0</v>
@@ -5597,8 +5765,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,77 +5854,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>327000</v>
+      </c>
+      <c r="E72" s="3">
         <v>250000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>215000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>148000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>79000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-11000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-36000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-90000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-138000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-164000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-186000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-214000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-255000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-237000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-252000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-271000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-292000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-284000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-262000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-289000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-325000</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5763,14 +5937,17 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC72" s="3">
-        <v>0</v>
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6032,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6121,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,77 +6210,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3171000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2982000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2953000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2967000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2835000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2301000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2071000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2232000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2247000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2165000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2127000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2150000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2156000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2278000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2323000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2297000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1828000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1791000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1558000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1598000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1565000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1525000</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6113,8 +6299,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6388,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43159</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E81" s="3">
         <v>35000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>67000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>69000</v>
       </c>
       <c r="G81" s="3">
         <v>69000</v>
       </c>
       <c r="H81" s="3">
+        <v>69000</v>
+      </c>
+      <c r="I81" s="3">
         <v>45000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>25000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>54000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>48000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>26000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>17000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-169000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>21000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-244000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>27000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>36000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-194000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-153000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>12000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>53000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>21000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-159600</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,94 +6606,98 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E83" s="3">
         <v>19000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>20000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>21000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>19000</v>
       </c>
       <c r="H83" s="3">
         <v>19000</v>
       </c>
       <c r="I83" s="3">
+        <v>19000</v>
+      </c>
+      <c r="J83" s="3">
         <v>17000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>22000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>19000</v>
       </c>
       <c r="L83" s="3">
         <v>19000</v>
       </c>
       <c r="M83" s="3">
+        <v>19000</v>
+      </c>
+      <c r="N83" s="3">
         <v>79000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>73000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>76000</v>
       </c>
       <c r="P83" s="3">
         <v>76000</v>
       </c>
       <c r="Q83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="R83" s="3">
         <v>48000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>52000</v>
       </c>
       <c r="S83" s="3">
         <v>52000</v>
       </c>
       <c r="T83" s="3">
+        <v>52000</v>
+      </c>
+      <c r="U83" s="3">
         <v>50000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>67000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>52000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>74000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>70000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>69000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>27000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>26000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>25000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6782,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6871,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6960,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7049,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,94 +7138,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E89" s="3">
         <v>62000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>283000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>220000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>110000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>297000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>144000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>74000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>188000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>146000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>54000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-118000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>114000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>49000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-13000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>32000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>167000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>97000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>177000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>55000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>150000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>92000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>28000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>25000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>40000</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,19 +7262,20 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-22000</v>
       </c>
       <c r="G91" s="3">
         <v>-22000</v>
@@ -7066,70 +7287,73 @@
         <v>-22000</v>
       </c>
       <c r="J91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-18000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-25000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-21000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-26000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-22000</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-12000</v>
       </c>
       <c r="Q91" s="3">
         <v>-12000</v>
       </c>
       <c r="R91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="S91" s="3">
         <v>-9000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-16000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-18000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-14000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6000</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-11000</v>
       </c>
       <c r="Y91" s="3">
         <v>-11000</v>
       </c>
       <c r="Z91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7438,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,94 +7527,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-126000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-149000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-57000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-601000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-55000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>30000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-28000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2884000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-40000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-46000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-23000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-323000</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-1000</v>
       </c>
       <c r="W94" s="3">
         <v>-1000</v>
       </c>
       <c r="X94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1728000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-22000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>18600</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7651,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7450,8 +7684,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7504,8 +7738,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7827,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7916,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,262 +8005,274 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-98000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-103000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>570000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-213000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-279000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-21000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-16000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-216000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-17000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-45000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1831000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>288000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>442000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-36000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>223000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>200000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-5000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-235000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>139000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1398000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>25000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>7000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>2000</v>
       </c>
       <c r="H101" s="3">
         <v>2000</v>
       </c>
       <c r="I101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J101" s="3">
         <v>8000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-7000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>8000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-8000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-7000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>4000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>3</v>
+      <c r="AC101" s="3">
+        <v>0</v>
       </c>
       <c r="AD101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-40000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>163000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>78000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-232000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>18000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>92000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-242000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>209000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>65000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1173000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>361000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>441000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-59000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>233000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>48000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>90000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-59000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>180000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-181000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>107000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-13000</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
   <si>
     <t>APG</t>
   </si>
@@ -656,417 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43159</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2117000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2085000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1990000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1719000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1861000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1826000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1730000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1601000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1759000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1784000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1771000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1614000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1703000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1735000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1649000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1471000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1112000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1047000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>978000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>803000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>882000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>958000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>889000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>858000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>985000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1118000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1067000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>922000</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1439000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1433000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1375000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1177000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1286000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1259000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1186000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1109000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1251000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1273000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1275000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1189000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1237000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1293000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1212000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1095000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>838000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>795000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>746000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>622000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>684000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>736000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>692000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>696000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>787000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>885000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>859000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>759000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>400</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>678000</v>
+      </c>
+      <c r="E10" s="3">
         <v>652000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>615000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>542000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>575000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>567000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>544000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>492000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>508000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>511000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>496000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>425000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>466000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>442000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>437000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>376000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>274000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>252000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>232000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>181000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>198000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>222000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>197000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>162000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>198000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>233000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>208000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>163000</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1099,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1191,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1283,111 +1299,117 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>29000</v>
+        <v>47000</v>
       </c>
       <c r="E14" s="3">
         <v>29000</v>
       </c>
       <c r="F14" s="3">
+        <v>29000</v>
+      </c>
+      <c r="G14" s="3">
         <v>15000</v>
       </c>
-      <c r="G14" s="3">
-        <v>7000</v>
-      </c>
       <c r="H14" s="3">
+        <v>9000</v>
+      </c>
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>23000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>22000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>3000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>12000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>11000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>24000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>9000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>208000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>12000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>3</v>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E15" s="3">
         <v>56000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>55000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>57000</v>
       </c>
       <c r="G15" s="3">
         <v>57000</v>
@@ -1396,40 +1418,40 @@
         <v>57000</v>
       </c>
       <c r="I15" s="3">
+        <v>57000</v>
+      </c>
+      <c r="J15" s="3">
         <v>52000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>50000</v>
       </c>
       <c r="K15" s="3">
         <v>50000</v>
       </c>
       <c r="L15" s="3">
+        <v>50000</v>
+      </c>
+      <c r="M15" s="3">
         <v>49000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>50000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>48000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>54000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>36000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>53000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>54000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>32000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>30000</v>
       </c>
       <c r="U15" s="3">
         <v>30000</v>
@@ -1441,34 +1463,37 @@
         <v>30000</v>
       </c>
       <c r="X15" s="3">
+        <v>30000</v>
+      </c>
+      <c r="Y15" s="3">
         <v>25000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>28000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>30000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>29000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>8000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>9000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>25000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>200</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1498,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1911000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1898000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1823000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1620000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1747000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1744000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1687000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1600000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1505000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1662000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1677000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1661000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1538000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1654000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1669000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1590000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1478000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1062000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1006000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>940000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>805000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>903000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>896000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>858000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1092000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1146000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1105000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1004000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>896000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>164900</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>206000</v>
+      </c>
+      <c r="E18" s="3">
         <v>187000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>167000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>99000</v>
       </c>
-      <c r="G18" s="3">
-        <v>114000</v>
-      </c>
       <c r="H18" s="3">
+        <v>117000</v>
+      </c>
+      <c r="I18" s="3">
         <v>139000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>130000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>96000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>97000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>107000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>110000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>76000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>49000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>66000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>59000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>50000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>41000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>38000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-21000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>62000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>31000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-234000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-161000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>13000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>63000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>26000</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1716,468 +1748,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-7000</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-2000</v>
       </c>
       <c r="J20" s="3">
         <v>-2000</v>
       </c>
       <c r="K20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-26000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>13000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>14000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>13000</v>
       </c>
       <c r="Q20" s="3">
         <v>13000</v>
       </c>
       <c r="R20" s="3">
+        <v>13000</v>
+      </c>
+      <c r="S20" s="3">
         <v>11000</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>3000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>6000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>14000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>6000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>7000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>25000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>8000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2000</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>260000</v>
+      </c>
+      <c r="E21" s="3">
         <v>249000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>229000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>156000</v>
       </c>
-      <c r="G21" s="3">
-        <v>169000</v>
-      </c>
       <c r="H21" s="3">
+        <v>172000</v>
+      </c>
+      <c r="I21" s="3">
         <v>200000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>184000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>148000</v>
       </c>
       <c r="K21" s="3">
         <v>148000</v>
       </c>
       <c r="L21" s="3">
+        <v>148000</v>
+      </c>
+      <c r="M21" s="3">
         <v>182000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>147000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>126000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>142000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>152000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>148000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>80000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>98000</v>
-      </c>
-      <c r="T21" s="3">
-        <v>96000</v>
       </c>
       <c r="U21" s="3">
         <v>96000</v>
       </c>
       <c r="V21" s="3">
+        <v>96000</v>
+      </c>
+      <c r="W21" s="3">
         <v>51000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>60000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>120000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>112000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-161000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-67000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>48000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>90000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>53000</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E22" s="3">
         <v>34000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>37000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>38000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>36000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>41000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>35000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>34000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>33000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>37000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>38000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>37000</v>
       </c>
       <c r="O22" s="3">
         <v>37000</v>
       </c>
       <c r="P22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>33000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>28000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>27000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>17000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>14000</v>
       </c>
       <c r="U22" s="3">
         <v>14000</v>
       </c>
       <c r="V22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="W22" s="3">
         <v>15000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>11000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>13000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>14000</v>
       </c>
       <c r="Z22" s="3">
         <v>14000</v>
       </c>
       <c r="AA22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AB22" s="3">
         <v>15000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>7000</v>
       </c>
       <c r="AC22" s="3">
         <v>7000</v>
       </c>
       <c r="AD22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>6000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>159600</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>129000</v>
+      </c>
+      <c r="E23" s="3">
         <v>130000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>108000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>46000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>78000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>100000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>89000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>63000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>45000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>74000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>75000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>38000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>26000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>46000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>44000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-23000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>33000</v>
-      </c>
-      <c r="T23" s="3">
-        <v>30000</v>
       </c>
       <c r="U23" s="3">
         <v>30000</v>
       </c>
       <c r="V23" s="3">
+        <v>30000</v>
+      </c>
+      <c r="W23" s="3">
         <v>-14000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-18000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>55000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>24000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-245000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-151000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>14000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>57000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>22000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-159600</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E24" s="3">
         <v>37000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>31000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>11000</v>
       </c>
       <c r="G24" s="3">
         <v>11000</v>
       </c>
       <c r="H24" s="3">
+        <v>11000</v>
+      </c>
+      <c r="I24" s="3">
         <v>31000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>20000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>18000</v>
-      </c>
-      <c r="K24" s="3">
-        <v>20000</v>
       </c>
       <c r="L24" s="3">
         <v>20000</v>
       </c>
       <c r="M24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="N24" s="3">
         <v>27000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>18000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-16000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>18000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>11000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-6000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>28000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-51000</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>2000</v>
       </c>
       <c r="AB24" s="3">
         <v>2000</v>
       </c>
       <c r="AC24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AD24" s="3">
         <v>4000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-159600</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2268,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E26" s="3">
         <v>93000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>77000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>35000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>67000</v>
-      </c>
-      <c r="H26" s="3">
-        <v>69000</v>
       </c>
       <c r="I26" s="3">
         <v>69000</v>
       </c>
       <c r="J26" s="3">
+        <v>69000</v>
+      </c>
+      <c r="K26" s="3">
         <v>45000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>25000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>54000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>48000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>26000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>22000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>28000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>30000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>15000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>19000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>21000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-22000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>27000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>36000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-194000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-153000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>12000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>53000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>21000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-159600</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-472000</v>
+      </c>
+      <c r="E27" s="3">
         <v>84000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>69000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>31000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-28000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>62000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>69000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-327000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-236000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>35000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>28000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>12000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>11000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>17000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-18000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-169000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>19000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>21000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-244000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>27000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>36000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-194000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-153000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>12000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>53000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>21000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-159600</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2544,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2636,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2728,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2820,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E32" s="3">
         <v>6000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>7000</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>2000</v>
       </c>
       <c r="J32" s="3">
         <v>2000</v>
       </c>
       <c r="K32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>26000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-13000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-14000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-13000</v>
       </c>
       <c r="Q32" s="3">
         <v>-13000</v>
       </c>
       <c r="R32" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="S32" s="3">
         <v>-11000</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-3000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-6000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-14000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E33" s="3">
         <v>93000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>77000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>35000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>67000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>69000</v>
       </c>
       <c r="I33" s="3">
         <v>69000</v>
       </c>
       <c r="J33" s="3">
+        <v>69000</v>
+      </c>
+      <c r="K33" s="3">
         <v>45000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>25000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>54000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>48000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>26000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>17000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-18000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-169000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>19000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>21000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-244000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>27000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>36000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-194000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-153000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>53000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>21000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-159600</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3096,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E35" s="3">
         <v>93000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>77000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>35000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>67000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>69000</v>
       </c>
       <c r="I35" s="3">
         <v>69000</v>
       </c>
       <c r="J35" s="3">
+        <v>69000</v>
+      </c>
+      <c r="K35" s="3">
         <v>45000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>25000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>54000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>48000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>26000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>17000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-18000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-169000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>19000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>21000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-244000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>27000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>36000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-194000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-153000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>53000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>21000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-159600</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43159</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3319,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3353,83 +3438,84 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>912000</v>
+      </c>
+      <c r="E41" s="3">
         <v>555000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>432000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>460000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>499000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>487000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>324000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>247000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>479000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>461000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>368000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>363000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>605000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>395000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>330000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>315000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1188000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1128000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>686000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>745000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>515000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>467000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>377000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>436000</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3445,8 +3531,11 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3537,83 +3626,86 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2047000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2139000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2052000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1841000</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1897000</v>
       </c>
       <c r="H43" s="3">
         <v>1897000</v>
       </c>
       <c r="I43" s="3">
+        <v>1897000</v>
+      </c>
+      <c r="J43" s="3">
         <v>1823000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1714000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1831000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1810000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1827000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1711000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1772000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1760000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1712000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1636000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>984000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>947000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>848000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>747000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>781000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>906000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>891000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>913000</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3629,83 +3721,86 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E44" s="3">
         <v>148000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>154000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>150000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>143000</v>
-      </c>
-      <c r="H44" s="3">
-        <v>155000</v>
       </c>
       <c r="I44" s="3">
         <v>155000</v>
       </c>
       <c r="J44" s="3">
+        <v>155000</v>
+      </c>
+      <c r="K44" s="3">
         <v>148000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>150000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>155000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>170000</v>
-      </c>
-      <c r="N44" s="3">
-        <v>163000</v>
       </c>
       <c r="O44" s="3">
         <v>163000</v>
       </c>
       <c r="P44" s="3">
+        <v>163000</v>
+      </c>
+      <c r="Q44" s="3">
         <v>150000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>149000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>142000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>69000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>71000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>69000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>66000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>64000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>57000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>60000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>59000</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3721,8 +3816,11 @@
       <c r="AF44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3759,45 +3857,45 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>112000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>167000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>170000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>134000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>385000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>93000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>82000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>75000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>77000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>74000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>66000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>42000</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3813,83 +3911,86 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3229000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3006000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2798000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2586000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2658000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2691000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2454000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2232000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2582000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2652000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2532000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2364000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2652000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2472000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2361000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2227000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2626000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2239000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1685000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1633000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1437000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1504000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1394000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1450000</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3905,47 +4006,50 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3000</v>
+        <v>7000</v>
       </c>
       <c r="E47" s="3">
         <v>3000</v>
       </c>
       <c r="F47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G47" s="3">
         <v>12000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3">
         <v>6000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>29000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>27000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>42000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>31000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8000</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -3997,83 +4101,86 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>698000</v>
+      </c>
+      <c r="E48" s="3">
         <v>674000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>672000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>642000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>647000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>651000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>634000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>609000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>618000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>604000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>639000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>621000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>629000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>608000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>614000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>628000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>427000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>439000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>453000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>459000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>462000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>452000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>467000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>500000</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4089,83 +4196,86 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4751000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4786000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4798000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4575000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4554000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4663000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4598000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4020000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4091000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4028000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4147000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4139000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4166000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4010000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4254000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4492000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1988000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1996000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1991000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2008000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2047000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1772000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1799000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1836000</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4181,8 +4291,11 @@
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4273,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4365,83 +4481,86 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>211000</v>
+      </c>
+      <c r="E52" s="3">
         <v>200000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>193000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>219000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>236000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>166000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>196000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>189000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>175000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>516000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>519000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>523000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>644000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>851000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>825000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>795000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>118000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>109000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>114000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>118000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>119000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>98000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>110000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>100000</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4457,8 +4576,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4549,83 +4671,86 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8936000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8721000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8539000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8098000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8152000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8245000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7961000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7192000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7590000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7949000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7974000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7766000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8091000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7941000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8054000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8142000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5159000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4783000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4243000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4218000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4065000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3826000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3770000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3886000</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4641,8 +4766,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4675,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4709,83 +4838,84 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>526000</v>
+      </c>
+      <c r="E57" s="3">
         <v>537000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>524000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>450000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>497000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>454000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>424000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>382000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>472000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>431000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>473000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>442000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>490000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>469000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>448000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>391000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>236000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>205000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>180000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>167000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>150000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>142000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>155000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>152000</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4801,83 +4931,86 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E58" s="3">
         <v>99000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>100000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>95000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>94000</v>
       </c>
       <c r="H58" s="3">
         <v>94000</v>
       </c>
       <c r="I58" s="3">
+        <v>94000</v>
+      </c>
+      <c r="J58" s="3">
         <v>86000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>180000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>80000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>328000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>79000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>78000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>212000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>28000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>29000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>42000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>63000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>49000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>44000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>45000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>244000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4893,83 +5026,86 @@
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>767000</v>
+      </c>
+      <c r="E59" s="3">
         <v>714000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>685000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>661000</v>
       </c>
-      <c r="G59" s="3">
-        <v>625000</v>
-      </c>
       <c r="H59" s="3">
+        <v>610000</v>
+      </c>
+      <c r="I59" s="3">
         <v>608000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>590000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>587000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>548000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>515000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>523000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>518000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1219000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1043000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>998000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>971000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>603000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>558000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>508000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>551000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>642000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>648000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>621000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>523000</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4985,83 +5121,86 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2150000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2031000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1933000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1762000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1885000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1781000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1662000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1654000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1807000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1899000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1651000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1549000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1921000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1523000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1453000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1367000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>867000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>792000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>730000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>781000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>841000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>834000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>821000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>919000</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5077,83 +5216,86 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2969000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2953000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2959000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2942000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2941000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3044000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3029000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2797000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2494000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2512000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2758000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2743000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2595000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2791000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2823000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2819000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1845000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1548000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1538000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1475000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1493000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1248000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1254000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1260000</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5169,83 +5311,86 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E62" s="3">
         <v>190000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>205000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>155000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>85000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>153000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>149000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>156000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>90000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>132000</v>
       </c>
       <c r="M62" s="3">
         <v>132000</v>
       </c>
       <c r="N62" s="3">
+        <v>132000</v>
+      </c>
+      <c r="O62" s="3">
         <v>130000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>651000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>680000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>825000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>881000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>124000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>146000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>147000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>171000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>173000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>146000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>130000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>182000</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5261,8 +5406,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5353,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5445,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5537,83 +5691,86 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5528000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5445000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5368000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5116000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5199000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5278000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5126000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4891000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4722000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4920000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4930000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4804000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5167000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4994000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5101000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5067000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2836000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2486000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2415000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2427000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2507000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2228000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2205000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2361000</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5629,8 +5786,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5663,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5755,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5847,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5874,7 +6041,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
-        <v>797000</v>
+        <v>0</v>
       </c>
       <c r="L70" s="3">
         <v>797000</v>
@@ -5898,7 +6065,7 @@
         <v>797000</v>
       </c>
       <c r="S70" s="3">
-        <v>0</v>
+        <v>797000</v>
       </c>
       <c r="T70" s="3">
         <v>0</v>
@@ -5939,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6031,83 +6201,86 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>517000</v>
+      </c>
+      <c r="E72" s="3">
         <v>420000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>327000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>250000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>215000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>148000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>79000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-11000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-36000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-90000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-138000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-164000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-186000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-214000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-255000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-237000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-252000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-271000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-292000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-284000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-262000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-289000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-325000</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6117,14 +6290,17 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE72" s="3">
-        <v>0</v>
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6215,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6307,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6399,83 +6581,86 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3408000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3276000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3171000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2982000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2953000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2967000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2835000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2301000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2071000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2232000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2247000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2165000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2127000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2150000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2156000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2278000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2323000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2297000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1828000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1791000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1558000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1598000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1565000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1525000</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6491,8 +6676,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6583,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43159</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E81" s="3">
         <v>93000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>77000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>35000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>67000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>69000</v>
       </c>
       <c r="I81" s="3">
         <v>69000</v>
       </c>
       <c r="J81" s="3">
+        <v>69000</v>
+      </c>
+      <c r="K81" s="3">
         <v>45000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>25000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>54000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>48000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>26000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>17000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-18000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-169000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>19000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>21000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-244000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>27000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>36000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-194000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-153000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>53000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>21000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-159600</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6806,100 +7003,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E83" s="3">
         <v>21000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>20000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>19000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>20000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>21000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>19000</v>
       </c>
       <c r="J83" s="3">
         <v>19000</v>
       </c>
       <c r="K83" s="3">
+        <v>19000</v>
+      </c>
+      <c r="L83" s="3">
         <v>17000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>22000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>19000</v>
       </c>
       <c r="N83" s="3">
         <v>19000</v>
       </c>
       <c r="O83" s="3">
+        <v>19000</v>
+      </c>
+      <c r="P83" s="3">
         <v>79000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>73000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>76000</v>
       </c>
       <c r="R83" s="3">
         <v>76000</v>
       </c>
       <c r="S83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="T83" s="3">
         <v>48000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>52000</v>
       </c>
       <c r="U83" s="3">
         <v>52000</v>
       </c>
       <c r="V83" s="3">
+        <v>52000</v>
+      </c>
+      <c r="W83" s="3">
         <v>50000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>67000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>52000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>74000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>70000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>69000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>27000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>26000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>25000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6990,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7082,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7174,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7266,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7358,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>382000</v>
+      </c>
+      <c r="E89" s="3">
         <v>232000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>83000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>62000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>283000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>220000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>110000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>297000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>144000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>74000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>188000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>146000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>54000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-118000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>114000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>49000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-13000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>32000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>167000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>97000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>177000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>55000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>150000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>92000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>28000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>25000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>40000</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7484,25 +7703,26 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-31000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-27000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-22000</v>
       </c>
       <c r="I91" s="3">
         <v>-22000</v>
@@ -7514,70 +7734,73 @@
         <v>-22000</v>
       </c>
       <c r="L91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="M91" s="3">
         <v>-18000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-21000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-19000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-22000</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-12000</v>
       </c>
       <c r="S91" s="3">
         <v>-12000</v>
       </c>
       <c r="T91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="U91" s="3">
         <v>-9000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-16000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-18000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-14000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6000</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-11000</v>
       </c>
       <c r="AA91" s="3">
         <v>-11000</v>
       </c>
       <c r="AB91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7668,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7760,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-91000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-126000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-149000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-57000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-601000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-55000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-27000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>30000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-28000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-19000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2884000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-40000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-46000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-23000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-323000</v>
-      </c>
-      <c r="X94" s="3">
-        <v>-1000</v>
       </c>
       <c r="Y94" s="3">
         <v>-1000</v>
       </c>
       <c r="Z94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1728000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-22000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>18600</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7886,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7924,8 +8157,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7978,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8070,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8162,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8254,280 +8496,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-15000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-98000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-103000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>570000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-213000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-279000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-21000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-16000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-216000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-17000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-45000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-13000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1831000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>288000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>442000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-36000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>223000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>200000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-235000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>139000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1398000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>25000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E101" s="3">
         <v>9000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>7000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5000</v>
-      </c>
-      <c r="I101" s="3">
-        <v>2000</v>
       </c>
       <c r="J101" s="3">
         <v>2000</v>
       </c>
       <c r="K101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L101" s="3">
         <v>8000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-7000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>8000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-7000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>3</v>
+      <c r="AE101" s="3">
+        <v>0</v>
       </c>
       <c r="AF101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>357000</v>
+      </c>
+      <c r="E102" s="3">
         <v>123000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-28000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-40000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>163000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>78000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-232000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>18000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>92000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-242000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>209000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>65000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1173000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>361000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>441000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-59000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>233000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>48000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>90000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-59000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>180000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-181000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>107000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>APG</t>
   </si>
@@ -656,429 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43159</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1982000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2117000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2085000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1990000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1719000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1861000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1826000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1730000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1601000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1759000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1784000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1771000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1614000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1703000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1735000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1649000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1471000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1112000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1047000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>978000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>803000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>882000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>958000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>889000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>858000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>985000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1118000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1067000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>922000</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1362000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1439000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1433000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1375000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1177000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1286000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1259000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1186000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1109000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1251000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1273000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1275000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1189000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1237000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1293000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1212000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1095000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>838000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>795000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>746000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>622000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>684000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>736000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>692000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>696000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>787000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>885000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>859000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>759000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>400</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>620000</v>
+      </c>
+      <c r="E10" s="3">
         <v>678000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>652000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>615000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>542000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>575000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>567000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>544000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>492000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>508000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>511000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>496000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>425000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>466000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>442000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>437000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>376000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>274000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>252000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>232000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>181000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>198000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>222000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>197000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>162000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>198000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>233000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>208000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>163000</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1125,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1221,11 @@
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,117 +1319,123 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E14" s="3">
         <v>47000</v>
-      </c>
-      <c r="E14" s="3">
-        <v>29000</v>
       </c>
       <c r="F14" s="3">
         <v>29000</v>
       </c>
       <c r="G14" s="3">
+        <v>29000</v>
+      </c>
+      <c r="H14" s="3">
         <v>15000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>9000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>23000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>22000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>3000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>12000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>11000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>24000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>9000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>208000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>12000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>3</v>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E15" s="3">
         <v>60000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>56000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>55000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>57000</v>
       </c>
       <c r="H15" s="3">
         <v>57000</v>
@@ -1421,40 +1444,40 @@
         <v>57000</v>
       </c>
       <c r="J15" s="3">
+        <v>57000</v>
+      </c>
+      <c r="K15" s="3">
         <v>52000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>50000</v>
       </c>
       <c r="L15" s="3">
         <v>50000</v>
       </c>
       <c r="M15" s="3">
+        <v>50000</v>
+      </c>
+      <c r="N15" s="3">
         <v>49000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>50000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>48000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>54000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>36000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>53000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>54000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>32000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>30000</v>
       </c>
       <c r="V15" s="3">
         <v>30000</v>
@@ -1466,34 +1489,37 @@
         <v>30000</v>
       </c>
       <c r="Y15" s="3">
+        <v>30000</v>
+      </c>
+      <c r="Z15" s="3">
         <v>25000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>28000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>30000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>29000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>8000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>9000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>25000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>200</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1550,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1838000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1911000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1898000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1823000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1620000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1624000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1744000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1687000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1600000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1505000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1662000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1677000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1661000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1538000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1654000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1669000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1590000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1478000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1062000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1006000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>940000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>805000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>903000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>896000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>858000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1092000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1146000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1105000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1004000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>896000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>164900</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E18" s="3">
         <v>206000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>187000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>167000</v>
       </c>
-      <c r="G18" s="3">
-        <v>99000</v>
-      </c>
       <c r="H18" s="3">
+        <v>95000</v>
+      </c>
+      <c r="I18" s="3">
         <v>117000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>139000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>130000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>96000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>97000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>107000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>110000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>76000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>49000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>66000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>59000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>50000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>41000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>38000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>62000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>31000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-234000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-161000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>63000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>26000</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,483 +1782,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>6000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7000</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I20" s="3">
         <v>2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-2000</v>
       </c>
       <c r="K20" s="3">
         <v>-2000</v>
       </c>
       <c r="L20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-26000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>13000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>14000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>13000</v>
       </c>
       <c r="R20" s="3">
         <v>13000</v>
       </c>
       <c r="S20" s="3">
+        <v>13000</v>
+      </c>
+      <c r="T20" s="3">
         <v>11000</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>3000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>6000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>14000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>6000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>7000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>25000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>8000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2000</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>208000</v>
+      </c>
+      <c r="E21" s="3">
         <v>260000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>249000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>229000</v>
       </c>
-      <c r="G21" s="3">
-        <v>156000</v>
-      </c>
       <c r="H21" s="3">
+        <v>155000</v>
+      </c>
+      <c r="I21" s="3">
         <v>172000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>200000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>184000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>148000</v>
       </c>
       <c r="L21" s="3">
         <v>148000</v>
       </c>
       <c r="M21" s="3">
+        <v>148000</v>
+      </c>
+      <c r="N21" s="3">
         <v>182000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>147000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>126000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>142000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>152000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>148000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>80000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>98000</v>
-      </c>
-      <c r="U21" s="3">
-        <v>96000</v>
       </c>
       <c r="V21" s="3">
         <v>96000</v>
       </c>
       <c r="W21" s="3">
+        <v>96000</v>
+      </c>
+      <c r="X21" s="3">
         <v>51000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>60000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>120000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>112000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-161000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-67000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>48000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>90000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>53000</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E22" s="3">
         <v>32000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>34000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>37000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>38000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>36000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>41000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>35000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>34000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>33000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>37000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>38000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>37000</v>
       </c>
       <c r="P22" s="3">
         <v>37000</v>
       </c>
       <c r="Q22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="R22" s="3">
         <v>33000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>28000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>27000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>17000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>14000</v>
       </c>
       <c r="V22" s="3">
         <v>14000</v>
       </c>
       <c r="W22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="X22" s="3">
         <v>15000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>11000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>13000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>14000</v>
       </c>
       <c r="AA22" s="3">
         <v>14000</v>
       </c>
       <c r="AB22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>15000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>7000</v>
       </c>
       <c r="AD22" s="3">
         <v>7000</v>
       </c>
       <c r="AE22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>6000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>159600</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E23" s="3">
         <v>129000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>130000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>108000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>46000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>78000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>100000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>89000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>63000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>45000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>74000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>75000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>38000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>26000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>46000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>44000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-23000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>33000</v>
-      </c>
-      <c r="U23" s="3">
-        <v>30000</v>
       </c>
       <c r="V23" s="3">
         <v>30000</v>
       </c>
       <c r="W23" s="3">
+        <v>30000</v>
+      </c>
+      <c r="X23" s="3">
         <v>-14000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>55000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>24000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-245000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-151000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>14000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>57000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>22000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-159600</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E24" s="3">
         <v>32000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>37000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>31000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>11000</v>
       </c>
       <c r="H24" s="3">
         <v>11000</v>
       </c>
       <c r="I24" s="3">
+        <v>11000</v>
+      </c>
+      <c r="J24" s="3">
         <v>31000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>20000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>18000</v>
-      </c>
-      <c r="L24" s="3">
-        <v>20000</v>
       </c>
       <c r="M24" s="3">
         <v>20000</v>
       </c>
       <c r="N24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="O24" s="3">
         <v>27000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>12000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>18000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>14000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-16000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>18000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>11000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>9000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-6000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>28000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-51000</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>2000</v>
       </c>
       <c r="AC24" s="3">
         <v>2000</v>
       </c>
       <c r="AD24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AE24" s="3">
         <v>4000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-159600</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E26" s="3">
         <v>97000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>93000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>77000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>35000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>67000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>69000</v>
       </c>
       <c r="J26" s="3">
         <v>69000</v>
       </c>
       <c r="K26" s="3">
+        <v>69000</v>
+      </c>
+      <c r="L26" s="3">
         <v>45000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>25000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>54000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>48000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>26000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>22000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>28000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>30000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>15000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>19000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>21000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>27000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>36000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-194000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-153000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>12000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>53000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>21000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-159600</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-472000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>84000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>69000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>31000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-28000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>62000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>69000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-327000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-236000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>35000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>28000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>12000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>11000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>17000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-18000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-169000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>19000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>21000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-244000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>27000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>36000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-194000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-153000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>12000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>53000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>21000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-159600</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +2956,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7000</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>2000</v>
       </c>
       <c r="K32" s="3">
         <v>2000</v>
       </c>
       <c r="L32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>26000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-13000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-14000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-13000</v>
       </c>
       <c r="R32" s="3">
         <v>-13000</v>
       </c>
       <c r="S32" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="T32" s="3">
         <v>-11000</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-3000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-6000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E33" s="3">
         <v>97000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>93000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>77000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>35000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>67000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>69000</v>
       </c>
       <c r="J33" s="3">
         <v>69000</v>
       </c>
       <c r="K33" s="3">
+        <v>69000</v>
+      </c>
+      <c r="L33" s="3">
         <v>45000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>25000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>54000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>48000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>26000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>11000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>17000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-18000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-169000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>19000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>21000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-244000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>27000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>36000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-194000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-153000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>12000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>53000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>21000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-159600</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E35" s="3">
         <v>97000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>93000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>77000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>35000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>67000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>69000</v>
       </c>
       <c r="J35" s="3">
         <v>69000</v>
       </c>
       <c r="K35" s="3">
+        <v>69000</v>
+      </c>
+      <c r="L35" s="3">
         <v>45000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>25000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>54000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>48000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>26000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>11000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>17000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-18000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-169000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>19000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>21000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-244000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>27000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>36000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-194000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-153000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>12000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>53000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>21000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-159600</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43159</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,86 +3525,87 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>645000</v>
+      </c>
+      <c r="E41" s="3">
         <v>912000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>555000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>432000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>460000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>499000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>487000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>324000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>247000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>479000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>461000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>368000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>363000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>605000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>395000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>330000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>315000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1188000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1128000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>686000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>745000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>515000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>467000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>377000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>436000</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,8 +3621,11 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,86 +3719,89 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2083000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2047000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2139000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2052000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1841000</v>
-      </c>
-      <c r="H43" s="3">
-        <v>1897000</v>
       </c>
       <c r="I43" s="3">
         <v>1897000</v>
       </c>
       <c r="J43" s="3">
+        <v>1897000</v>
+      </c>
+      <c r="K43" s="3">
         <v>1823000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1714000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1831000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1810000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1827000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1711000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1772000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1760000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1712000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1636000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>984000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>947000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>848000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>747000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>781000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>906000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>891000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>913000</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3724,86 +3817,89 @@
       <c r="AG43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E44" s="3">
         <v>145000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>148000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>154000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>150000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>143000</v>
-      </c>
-      <c r="I44" s="3">
-        <v>155000</v>
       </c>
       <c r="J44" s="3">
         <v>155000</v>
       </c>
       <c r="K44" s="3">
+        <v>155000</v>
+      </c>
+      <c r="L44" s="3">
         <v>148000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>150000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>155000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>170000</v>
-      </c>
-      <c r="O44" s="3">
-        <v>163000</v>
       </c>
       <c r="P44" s="3">
         <v>163000</v>
       </c>
       <c r="Q44" s="3">
+        <v>163000</v>
+      </c>
+      <c r="R44" s="3">
         <v>150000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>149000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>142000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>69000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>71000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>69000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>66000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>64000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>57000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>60000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>59000</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3819,8 +3915,11 @@
       <c r="AG44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3860,45 +3959,45 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>112000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>167000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>170000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>134000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>385000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>93000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>82000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>75000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>77000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>74000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>66000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>42000</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3914,86 +4013,89 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3024000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3229000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3006000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2798000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2586000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2658000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2691000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2454000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2232000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2582000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2652000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2532000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2364000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2652000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2472000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2361000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2227000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2626000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2239000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1685000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1633000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1437000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1504000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1394000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1450000</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4009,50 +4111,53 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E47" s="3">
         <v>7000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>3000</v>
       </c>
       <c r="F47" s="3">
         <v>3000</v>
       </c>
       <c r="G47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H47" s="3">
         <v>12000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>6000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>29000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>27000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>42000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>31000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8000</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4104,86 +4209,89 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>695000</v>
+      </c>
+      <c r="E48" s="3">
         <v>698000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>674000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>672000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>642000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>647000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>651000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>634000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>609000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>618000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>604000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>639000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>621000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>629000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>608000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>614000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>628000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>427000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>439000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>453000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>459000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>462000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>452000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>467000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>500000</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4199,86 +4307,89 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4949000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4751000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4786000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4798000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4575000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4554000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4663000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4598000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4020000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4091000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4028000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4147000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4139000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4166000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4010000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4254000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4492000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1988000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1996000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1991000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2008000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2047000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1772000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1799000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1836000</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4294,8 +4405,11 @@
       <c r="AG49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,86 +4601,89 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E52" s="3">
         <v>211000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>200000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>193000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>219000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>236000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>166000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>196000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>189000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>175000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>516000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>519000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>523000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>644000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>851000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>825000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>795000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>118000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>109000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>114000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>118000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>119000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>98000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>110000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>100000</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4579,8 +4699,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,86 +4797,89 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8966000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8936000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8721000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8539000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8098000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8152000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8245000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7961000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7192000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7590000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7949000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7974000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7766000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8091000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7941000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8054000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8142000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5159000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4783000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4243000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4218000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4065000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3826000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3770000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3886000</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4769,8 +4895,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,86 +4969,87 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>506000</v>
+      </c>
+      <c r="E57" s="3">
         <v>526000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>537000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>524000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>450000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>497000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>454000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>424000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>382000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>472000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>431000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>473000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>442000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>490000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>469000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>448000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>391000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>236000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>205000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>180000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>167000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>150000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>142000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>155000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>152000</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4934,86 +5065,89 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E58" s="3">
         <v>103000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>99000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>100000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>95000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>94000</v>
       </c>
       <c r="I58" s="3">
         <v>94000</v>
       </c>
       <c r="J58" s="3">
+        <v>94000</v>
+      </c>
+      <c r="K58" s="3">
         <v>86000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>180000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>80000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>328000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>79000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>78000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>212000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>11000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>28000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>29000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>42000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>63000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>49000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>44000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>45000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>244000</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5029,86 +5163,89 @@
       <c r="AG58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>859000</v>
+      </c>
+      <c r="E59" s="3">
         <v>767000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>714000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>685000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>661000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>610000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>608000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>590000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>587000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>548000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>515000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>523000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>518000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1219000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1043000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>998000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>971000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>603000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>558000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>508000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>551000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>642000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>648000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>621000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>523000</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5124,86 +5261,89 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2107000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2150000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2031000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1933000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1762000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1885000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1781000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1662000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1654000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1807000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1899000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1651000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1549000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1921000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1523000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1453000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1367000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>867000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>792000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>730000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>781000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>841000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>834000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>821000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>919000</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5219,86 +5359,89 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2969000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2953000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2959000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2942000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2941000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3044000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3029000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2797000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2494000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2512000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2758000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2743000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2595000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2791000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2823000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2819000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1845000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1548000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1538000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1475000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1493000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1248000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1254000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1260000</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5314,86 +5457,89 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E62" s="3">
         <v>111000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>190000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>205000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>155000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>85000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>153000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>149000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>156000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>90000</v>
-      </c>
-      <c r="M62" s="3">
-        <v>132000</v>
       </c>
       <c r="N62" s="3">
         <v>132000</v>
       </c>
       <c r="O62" s="3">
+        <v>132000</v>
+      </c>
+      <c r="P62" s="3">
         <v>130000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>651000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>680000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>825000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>881000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>124000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>146000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>147000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>171000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>173000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>146000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>130000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>182000</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5409,8 +5555,11 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,86 +5849,89 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5480000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5528000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5445000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5368000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5116000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5199000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5278000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5126000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4891000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4722000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4920000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4930000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4804000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5167000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4994000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5101000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5067000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2836000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2486000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2415000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2427000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2507000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2228000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2205000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2361000</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5789,8 +5947,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6044,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
-        <v>797000</v>
+        <v>0</v>
       </c>
       <c r="M70" s="3">
         <v>797000</v>
@@ -6068,7 +6236,7 @@
         <v>797000</v>
       </c>
       <c r="T70" s="3">
-        <v>0</v>
+        <v>797000</v>
       </c>
       <c r="U70" s="3">
         <v>0</v>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,86 +6375,89 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>574000</v>
+      </c>
+      <c r="E72" s="3">
         <v>517000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>420000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>327000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>250000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>215000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>148000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>79000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-11000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-36000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-90000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-138000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-164000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-186000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-214000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-255000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-237000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-252000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-271000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-292000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-284000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-262000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-289000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-325000</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6293,14 +6467,17 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF72" s="3">
-        <v>0</v>
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,86 +6767,89 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3486000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3408000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3276000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3171000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2982000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2953000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2967000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2835000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2301000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2071000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2232000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2247000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2165000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2127000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2150000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2156000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2278000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2323000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2297000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1828000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1791000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1558000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1598000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1565000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1525000</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6679,8 +6865,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43159</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E81" s="3">
         <v>97000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>93000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>77000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>35000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>67000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>69000</v>
       </c>
       <c r="J81" s="3">
         <v>69000</v>
       </c>
       <c r="K81" s="3">
+        <v>69000</v>
+      </c>
+      <c r="L81" s="3">
         <v>45000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>25000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>54000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>48000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>26000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>11000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>17000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-18000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-169000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>19000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>21000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-244000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>27000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>36000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-194000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-153000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>12000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>53000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>21000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-159600</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7202,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7013,94 +7212,97 @@
         <v>20000</v>
       </c>
       <c r="E83" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F83" s="3">
         <v>21000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>20000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>19000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>20000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>19000</v>
       </c>
       <c r="K83" s="3">
         <v>19000</v>
       </c>
       <c r="L83" s="3">
+        <v>19000</v>
+      </c>
+      <c r="M83" s="3">
         <v>17000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>22000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>19000</v>
       </c>
       <c r="O83" s="3">
         <v>19000</v>
       </c>
       <c r="P83" s="3">
+        <v>19000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>79000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>73000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>76000</v>
       </c>
       <c r="S83" s="3">
         <v>76000</v>
       </c>
       <c r="T83" s="3">
+        <v>76000</v>
+      </c>
+      <c r="U83" s="3">
         <v>48000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>52000</v>
       </c>
       <c r="V83" s="3">
         <v>52000</v>
       </c>
       <c r="W83" s="3">
+        <v>52000</v>
+      </c>
+      <c r="X83" s="3">
         <v>50000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>67000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>52000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>74000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>70000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>69000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>27000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>26000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>25000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E89" s="3">
         <v>382000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>232000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>83000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>62000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>283000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>220000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>110000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>297000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>144000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>74000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>188000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>146000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>54000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-118000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>114000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>49000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-13000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>32000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>167000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>97000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>177000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>55000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>150000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>92000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>28000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>25000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>40000</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,28 +7924,29 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-26000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-31000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-27000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-22000</v>
       </c>
       <c r="J91" s="3">
         <v>-22000</v>
@@ -7737,70 +7958,73 @@
         <v>-22000</v>
       </c>
       <c r="M91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="N91" s="3">
         <v>-18000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-25000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-21000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-26000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-22000</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-12000</v>
       </c>
       <c r="T91" s="3">
         <v>-12000</v>
       </c>
       <c r="U91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="V91" s="3">
         <v>-9000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-16000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-18000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6000</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-11000</v>
       </c>
       <c r="AB91" s="3">
         <v>-11000</v>
       </c>
       <c r="AC91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8216,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-305000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-91000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-126000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-149000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-57000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-601000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-26000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-55000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-27000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>30000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-28000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-19000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2884000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-40000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-46000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-12000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-23000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-323000</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>-1000</v>
       </c>
       <c r="Z94" s="3">
         <v>-1000</v>
       </c>
       <c r="AA94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1728000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-22000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>18600</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8352,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8160,8 +8394,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,289 +8742,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-15000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-98000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-103000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>570000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-213000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-279000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-21000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-16000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-216000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-45000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-13000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1831000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>288000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>442000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-36000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>223000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>200000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-235000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>139000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1398000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>25000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-19000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>2000</v>
       </c>
       <c r="K101" s="3">
         <v>2000</v>
       </c>
       <c r="L101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M101" s="3">
         <v>8000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-8000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-7000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>8000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-8000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-7000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-4000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>4000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>3</v>
+      <c r="AF101" s="3">
+        <v>0</v>
       </c>
       <c r="AG101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-268000</v>
+      </c>
+      <c r="E102" s="3">
         <v>357000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>123000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-28000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-40000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>163000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>78000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-232000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>18000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>92000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-242000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>209000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>65000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1173000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>361000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>441000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-59000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>233000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>48000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>90000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-59000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>180000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-181000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>107000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-13000</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
